--- a/reports/opportunity_report.xlsx
+++ b/reports/opportunity_report.xlsx
@@ -10,7 +10,7 @@
     <sheet name="SEO-GEO radar" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'SEO-GEO radar'!$A$1:$M$118</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'SEO-GEO radar'!$A$1:$M$158</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M118"/>
+  <dimension ref="A1:M158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -537,12 +537,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>استخدام متخصص سئو در دنیای ایده های تابان فناوری (داتک)</t>
+          <t>استخدام متخصص سئو در آنلاین جو</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>داتک</t>
+          <t>آنلاین جو</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>https://jobinja.ir/companies/dotech/jobs/h4/</t>
+          <t>https://jobinja.ir/companies/onlinejoo/jobs/2pq/</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -562,7 +562,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>تهران</t>
+          <t>ایران</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -577,7 +577,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-10-01 06:01</t>
+          <t>2026-10-07 06:01</t>
         </is>
       </c>
       <c r="J2" s="3" t="n">
@@ -585,7 +585,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>✓ Role: متخصص سئو | ✓ SEO | ✓ Remote</t>
+          <t>✓ Role: متخصص سئو | ✓ SEO | ✓ Remote | ✓ ایران</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -598,22 +598,22 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>استخدام متخصص سئو (SEO-دورکاری) در وبسایت ویزا 724</t>
+          <t>SEO &amp; Technical Search Manager – iGaming</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ویزا 724</t>
+          <t>Accelerate Finance &amp; Legal Recruitment</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>جستجوی وب (جابینجا)</t>
+          <t>LinkedIn Jobs — SEO</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>https://jobinja.ir/companies/visa724-com/jobs/RAmT/</t>
+          <t>https://www.linkedin.com/jobs/view/4474714421/</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -623,12 +623,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ایران</t>
+          <t>Sliema, Sliema, Malta (Remote)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Job</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -638,15 +638,15 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-10-01 06:01</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="n">
-        <v>72</v>
+          <t>2026-10-07 06:01</t>
+        </is>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>56</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>✓ Role: متخصص سئو | ✓ SEO | ✓ Search Console &amp; Analytics | ✓ Remote | ✓ ایران</t>
+          <t>✓ Title: SEO | ✓ SEO | ✓ Remote</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -659,22 +659,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>استخدام کارشناس سئو (دورکاری) در بی هیرو</t>
+          <t>Associate GEO and SEO Specialist</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>بی هیرو</t>
+          <t>MaintainX</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>جستجوی وب (جابینجا)</t>
+          <t>LinkedIn Jobs — SEO</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>https://jobinja.ir/companies/be-hero/jobs/CMa1/</t>
+          <t>https://www.linkedin.com/jobs/view/4472831639/</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ایران</t>
+          <t>Denver, Colorado, United States (Remote)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -699,15 +699,15 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-10-01 06:01</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="n">
-        <v>66</v>
+          <t>2026-10-07 06:01</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="n">
+        <v>81</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>✓ Role: کارشناس سئو | ✓ SEO | ✓ Remote | ✓ ایران</t>
+          <t>✓ Role: SEO Specialist | ✓ SEO | ✓ GEO / AI Search | ✓ Remote</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -720,22 +720,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>استخدام کارشناس سئو (SEO-دورکاری) در مارکت پیما</t>
+          <t>AI Search &amp; SEO Strategist</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>مارکت پیما</t>
+          <t>Henderson Scott</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>جستجوی وب (جابینجا)</t>
+          <t>LinkedIn Jobs — SEO</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>https://jobinja.ir/companies/marketpeima/jobs/Jkv/</t>
+          <t>https://www.linkedin.com/jobs/view/4476166254/</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -745,7 +745,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ایران</t>
+          <t>Malvern, Pennsylvania, United States (Remote)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -760,15 +760,15 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-10-01 06:01</t>
+          <t>2026-10-07 06:01</t>
         </is>
       </c>
       <c r="J5" s="4" t="n">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>✓ Role: کارشناس سئو | ✓ SEO | ✓ SEO Strategy &amp; Leadership | ✓ Remote | ✓ ایران</t>
+          <t>✓ Role: SEO Strategist | ✓ SEO | ✓ GEO / AI Search | ✓ Remote | ✓ Fresh</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -781,12 +781,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Technical SEO Specialist</t>
+          <t>SEO &amp; AI Search Visibility Specialist</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>OLX</t>
+          <t>BuzzyBooth</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4465089160/</t>
+          <t>https://www.linkedin.com/jobs/view/4476391372/</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Portugal (Remote)</t>
+          <t>Brazil (Remote)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -821,15 +821,15 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
+          <t>2026-10-07 06:01</t>
         </is>
       </c>
       <c r="J6" s="4" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>✓ Role: SEO Specialist | ✓ SEO | ✓ Technical &amp; On-page | ✓ Remote | ✓ Fresh</t>
+          <t>✓ Title: SEO | ✓ SEO | ✓ GEO / AI Search | ✓ Remote | ✓ Fresh</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -842,12 +842,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SEO &amp; Generative Engine Optimization Manager</t>
+          <t>Sr. Analyst, Organic Search - Local SEO Focus</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Shine</t>
+          <t>Augurian</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4471207490/</t>
+          <t>https://www.linkedin.com/jobs/view/4472590169/</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Madrid, Community of Madrid, Spain (Remote)</t>
+          <t>St Paul, Minnesota, United States (Remote)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -882,15 +882,15 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
-        </is>
-      </c>
-      <c r="J7" s="4" t="n">
-        <v>77</v>
+          <t>2026-10-07 06:01</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>56</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>✓ Title: SEO | ✓ SEO | ✓ GEO / AI Search | ✓ Remote | ✓ Fresh</t>
+          <t>✓ Title: SEO | ✓ SEO | ✓ Remote</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -903,12 +903,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SEO &amp; AI Search Manager H/F</t>
+          <t>Consultant·e SEO / GEO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Feu Vert France</t>
+          <t>Milestones</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4451407600/</t>
+          <t>https://www.linkedin.com/jobs/view/4473159094/</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Écully, Auvergne-Rhône-Alpes, France (Remote)</t>
+          <t>Paris, Île-de-France, France (Remote)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Job</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -943,15 +943,15 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
+          <t>2026-10-07 06:01</t>
         </is>
       </c>
       <c r="J8" s="4" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>✓ Title: SEO | ✓ SEO | ✓ GEO / AI Search | ✓ Remote | ✓ Fresh</t>
+          <t>✓ Title: SEO | ✓ SEO | ✓ GEO / AI Search | ✓ Remote</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -964,12 +964,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Account Executive, SEO</t>
+          <t>Senior SEO Consultant</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>WPP Media</t>
+          <t>WPP Enterprise Solutions</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4472177626/</t>
+          <t>https://www.linkedin.com/jobs/view/4475803338/</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -989,12 +989,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>London, England, United Kingdom (Remote)</t>
+          <t>Amsterdam, North Holland, Netherlands (Remote)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Job</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1004,15 +1004,15 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
-        </is>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
+          <t>2026-10-07 06:01</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="n">
+        <v>70</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>✗ Excluded: account executive</t>
+          <t>✓ Role: SEO Consultant | ✓ SEO | ✓ Remote | ✓ Fresh</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1025,12 +1025,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr SEO Consultant</t>
+          <t>SEO Strategist</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DealerOn</t>
+          <t>SJ Solutions &amp; Infotech - Website &amp; Product Development Company</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4473547285/</t>
+          <t>https://www.linkedin.com/jobs/view/4473632591/</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1050,12 +1050,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>United States (Remote)</t>
+          <t>Ludhiana, Punjab, India (Remote)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Job</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
+          <t>2026-10-07 06:01</t>
         </is>
       </c>
       <c r="J10" s="4" t="n">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>✓ Role: SEO Consultant | ✓ SEO | ✓ Remote | ✓ Fresh</t>
+          <t>✓ Role: SEO Strategist | ✓ SEO | ✓ Remote | ✓ Fresh</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1086,12 +1086,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Online-Consultant Schwerpunkt SEO &amp; GEO (all genders)</t>
+          <t>Consultant SEO / GEO Senior (H/F)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Publik. Agentur für Kommunikation GmbH (GPRA)</t>
+          <t>Yuri &amp; Neil</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4472193348/</t>
+          <t>https://www.linkedin.com/jobs/view/4472534126/</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mannheim, Baden-Württemberg, Germany (Remote)</t>
+          <t>Levallois-Perret, Île-de-France, France (Remote)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1126,15 +1126,15 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
+          <t>2026-10-07 06:01</t>
         </is>
       </c>
       <c r="J11" s="4" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>✓ Title: SEO | ✓ SEO | ✓ GEO / AI Search | ✓ Remote | ✓ Fresh</t>
+          <t>✓ Title: SEO | ✓ SEO | ✓ GEO / AI Search | ✓ Remote</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1147,12 +1147,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior SEO Strategist</t>
+          <t>Consultant SEO &amp; GEO – Expert Discover (H/F)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EITB Global Info Solutions Pty Ltd</t>
+          <t>Eskimoz</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4471263332/</t>
+          <t>https://www.linkedin.com/jobs/view/4473344412/</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1172,12 +1172,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Chennai, Tamil Nadu, India (Remote)</t>
+          <t>Boulogne-Billancourt, Île-de-France, France (Remote)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Job</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1187,15 +1187,15 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
+          <t>2026-10-07 06:01</t>
         </is>
       </c>
       <c r="J12" s="4" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>✓ Role: SEO Strategist | ✓ SEO | ✓ Remote | ✓ Fresh</t>
+          <t>✓ Title: SEO | ✓ SEO | ✓ GEO / AI Search | ✓ Remote</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1208,12 +1208,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SEO Strategist</t>
+          <t>Consultant SEO / GEO Confirmé (H/F)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Razorfish</t>
+          <t>Yuri &amp; Neil</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4471545623/</t>
+          <t>https://www.linkedin.com/jobs/view/4472533202/</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Chicago, Illinois, United States (Remote)</t>
+          <t>Levallois-Perret, Île-de-France, France (Remote)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Job</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1248,15 +1248,15 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
+          <t>2026-10-07 06:01</t>
         </is>
       </c>
       <c r="J13" s="4" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>✓ Role: SEO Strategist | ✓ SEO | ✓ Remote | ✓ Fresh</t>
+          <t>✓ Title: SEO | ✓ SEO | ✓ GEO / AI Search | ✓ Remote</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1269,12 +1269,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr. Strategist, SEO &amp; AI Discovery</t>
+          <t>SEO/GEO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>dentsu</t>
+          <t>LITY</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4470079280/</t>
+          <t>https://www.linkedin.com/jobs/view/4475810334/</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Chicago, Illinois, United States (Remote)</t>
+          <t>Paris, Île-de-France, France (Remote)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1309,15 +1309,15 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
-        </is>
-      </c>
-      <c r="J14" s="3" t="n">
-        <v>56</v>
+          <t>2026-10-07 06:01</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="n">
+        <v>77</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>✓ Title: SEO | ✓ SEO | ✓ Remote</t>
+          <t>✓ Title: SEO | ✓ SEO | ✓ GEO / AI Search | ✓ Remote | ✓ Fresh</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1330,12 +1330,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Consultant SEO &amp; GEO (CDI)</t>
+          <t>Senior SEO Manager (AI Visibility/GEO/AIO) (m/w/d)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Sonate</t>
+          <t>XXXLdigital – Part of XXXL Group</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4472134078/</t>
+          <t>https://www.linkedin.com/jobs/view/4434839295/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1355,12 +1355,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Paris, Île-de-France, France (Remote)</t>
+          <t>Berlin, Germany (Remote)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Job</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1370,15 +1370,15 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
+          <t>2026-10-07 06:01</t>
         </is>
       </c>
       <c r="J15" s="4" t="n">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>✓ Title: SEO | ✓ SEO | ✓ GEO / AI Search | ✓ Remote | ✓ Fresh</t>
+          <t>✓ Role: SEO Manager | ✓ SEO | ✓ GEO / AI Search | ✓ SEO Strategy &amp; Leadership | ✓ Remote</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1391,12 +1391,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior SEO / GEO Consultant (all genders)</t>
+          <t>Senior Technical SEO Manager</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>adesso SE</t>
+          <t>Proton</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4471599945/</t>
+          <t>https://www.linkedin.com/jobs/view/4439323459/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1416,12 +1416,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ulm, Baden-Württemberg, Germany (Remote)</t>
+          <t>London, England, United Kingdom (Remote)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Job</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1431,15 +1431,15 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
+          <t>2026-10-07 06:01</t>
         </is>
       </c>
       <c r="J16" s="4" t="n">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>✓ Title: SEO | ✓ SEO | ✓ GEO / AI Search | ✓ Remote | ✓ Fresh</t>
+          <t>✓ Role: SEO Manager | ✓ SEO | ✓ SEO Strategy &amp; Leadership | ✓ Technical &amp; On-page | ✓ Remote | ✓ Fresh</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1452,12 +1452,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior SEO / GEO Consultant (all genders)</t>
+          <t>Senior SEO Consultant</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>adesso SE</t>
+          <t>VML Enterprise Solutions</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4471910617/</t>
+          <t>https://www.linkedin.com/jobs/view/4473680396/</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1477,7 +1477,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stralsund, Mecklenburg-West Pomerania, Germany (Remote)</t>
+          <t>Amsterdam, North Holland, Netherlands (Remote)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1492,15 +1492,15 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
+          <t>2026-10-07 06:01</t>
         </is>
       </c>
       <c r="J17" s="4" t="n">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>✓ Title: SEO | ✓ SEO | ✓ GEO / AI Search | ✓ Remote | ✓ Fresh</t>
+          <t>✓ Role: SEO Consultant | ✓ SEO | ✓ Remote | ✓ Fresh</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1513,12 +1513,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior SEO Consultant</t>
+          <t>SEO Expert</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SlopeLift</t>
+          <t>DesignRush</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4472126314/</t>
+          <t>https://www.linkedin.com/jobs/view/4474148574/</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1538,12 +1538,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vienna, Austria (Remote)</t>
+          <t>Manchester Area, United Kingdom (Remote)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Job</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1553,7 +1553,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
+          <t>2026-10-07 06:01</t>
         </is>
       </c>
       <c r="J18" s="4" t="n">
@@ -1561,7 +1561,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>✓ Role: SEO Consultant | ✓ SEO | ✓ Remote | ✓ Fresh</t>
+          <t>✓ Role: SEO Expert | ✓ SEO | ✓ Remote | ✓ Fresh</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1574,12 +1574,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior SEO Manager</t>
+          <t>SEO Manager</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Jellyfish</t>
+          <t>PulteGroup</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4455925464/</t>
+          <t>https://www.linkedin.com/jobs/view/4409702685/</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1599,7 +1599,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>New York, United States (Remote)</t>
+          <t>Atlanta Metropolitan Area (Remote)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1614,15 +1614,15 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
+          <t>2026-10-07 06:01</t>
         </is>
       </c>
       <c r="J19" s="4" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>✓ Role: SEO Manager | ✓ SEO | ✓ SEO Strategy &amp; Leadership | ✓ Remote | ✓ Fresh</t>
+          <t>✓ Role: SEO Manager | ✓ SEO | ✓ SEO Strategy &amp; Leadership | ✓ Remote</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1635,12 +1635,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>(Senior) SEO &amp; GEO Manager (w/m/d)</t>
+          <t>SEO Team Lead</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>LAUDO</t>
+          <t>Liberty Marketing</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4471293441/</t>
+          <t>https://www.linkedin.com/jobs/view/4476342695/</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Berlin, Berlin, Germany (Remote)</t>
+          <t>United Kingdom (Remote)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1675,15 +1675,15 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
-        </is>
-      </c>
-      <c r="J20" s="4" t="n">
-        <v>77</v>
+          <t>2026-10-07 06:01</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="n">
+        <v>59</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>✓ Title: SEO | ✓ SEO | ✓ GEO / AI Search | ✓ Remote | ✓ Fresh</t>
+          <t>✓ Title: SEO | ✓ SEO | ✓ Remote | ✓ Fresh</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1696,12 +1696,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SEO Team Lead</t>
+          <t>Senior Content &amp; SEO Marketing Manager</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SHARDA CONSULTANCY SERVICES</t>
+          <t>Focus Partners</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4473215075/</t>
+          <t>https://www.linkedin.com/jobs/view/4456745038/</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Delhi, Delhi, India (Remote)</t>
+          <t>St Louis, Missouri, United States (Remote)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1736,15 +1736,15 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
-        </is>
-      </c>
-      <c r="J21" s="3" t="n">
-        <v>59</v>
+          <t>2026-10-07 06:01</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>✓ Title: SEO | ✓ SEO | ✓ Remote | ✓ Fresh</t>
+          <t>✗ Excluded: marketing manager</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1757,12 +1757,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior SEO Strategist - Madrid based</t>
+          <t>Sr. SEO Manager</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Fever</t>
+          <t>iCrossing</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4452571488/</t>
+          <t>https://www.linkedin.com/jobs/view/4437898425/</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rome, Latium, Italy (Remote)</t>
+          <t>Chicago, Illinois, United States (Remote)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1797,15 +1797,15 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
+          <t>2026-10-07 06:01</t>
         </is>
       </c>
       <c r="J22" s="4" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>✓ Role: SEO Strategist | ✓ SEO | ✓ Remote | ✓ Fresh</t>
+          <t>✓ Role: SEO Manager | ✓ SEO | ✓ SEO Strategy &amp; Leadership | ✓ Remote</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1818,12 +1818,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SEO &amp; GEO Lead</t>
+          <t>Sr. SEO Manager</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Verz Design</t>
+          <t>iCrossing</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4460990037/</t>
+          <t>https://www.linkedin.com/jobs/view/4437896568/</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Singapore, Singapore (Remote)</t>
+          <t>Scottsdale, Arizona, United States (Remote)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1858,15 +1858,15 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
+          <t>2026-10-07 06:01</t>
         </is>
       </c>
       <c r="J23" s="4" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>✓ Title: SEO | ✓ SEO | ✓ GEO / AI Search | ✓ Remote | ✓ Fresh</t>
+          <t>✓ Role: SEO Manager | ✓ SEO | ✓ SEO Strategy &amp; Leadership | ✓ Remote</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1879,12 +1879,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior SEO Manager (all genders) - Berlin</t>
+          <t>Senior SEO Manager (AI Visibility/GEO/AIO) (m/w/d)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Digitas Germany</t>
+          <t>XXXLdigital – Part of XXXL Group</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4462959564/</t>
+          <t>https://www.linkedin.com/jobs/view/4434829655/</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Berlin, Berlin, Germany (Remote)</t>
+          <t>Würzburg, Bavaria, Germany (Remote)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1919,15 +1919,15 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
+          <t>2026-10-07 06:01</t>
         </is>
       </c>
       <c r="J24" s="4" t="n">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>✓ Role: SEO Manager | ✓ SEO | ✓ SEO Strategy &amp; Leadership | ✓ Remote | ✓ Fresh</t>
+          <t>✓ Role: SEO Manager | ✓ SEO | ✓ GEO / AI Search | ✓ SEO Strategy &amp; Leadership | ✓ Remote</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -1940,12 +1940,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Manager (SEO)</t>
+          <t>Senior SEO Manager</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>EazyGrad</t>
+          <t>Fantastic Digital</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4471505014/</t>
+          <t>https://www.linkedin.com/jobs/view/4419238939/</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>New Delhi, Delhi, India (Remote)</t>
+          <t>Rishon LeZion, Center District, Israel (Remote)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1980,15 +1980,15 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
-        </is>
-      </c>
-      <c r="J25" s="3" t="n">
-        <v>59</v>
+          <t>2026-10-07 06:01</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="n">
+        <v>81</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>✓ Title: SEO | ✓ SEO | ✓ Remote | ✓ Fresh</t>
+          <t>✓ Role: SEO Manager | ✓ SEO | ✓ SEO Strategy &amp; Leadership | ✓ Remote | ✓ Fresh</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2001,12 +2001,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SEO Team Leader</t>
+          <t>Senior SEO Manager</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Matrix Web Infotech</t>
+          <t>Digitas UK</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4469727428/</t>
+          <t>https://www.linkedin.com/jobs/view/4428405203/</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Udaipur, Rajasthan, India (Remote)</t>
+          <t>London, England, United Kingdom (Remote)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2041,15 +2041,15 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
-        </is>
-      </c>
-      <c r="J26" s="3" t="n">
-        <v>59</v>
+          <t>2026-10-07 06:01</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="n">
+        <v>78</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>✓ Title: SEO | ✓ SEO | ✓ Remote | ✓ Fresh</t>
+          <t>✓ Role: SEO Manager | ✓ SEO | ✓ SEO Strategy &amp; Leadership | ✓ Remote</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2062,12 +2062,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior SEO Strategist</t>
+          <t>Senior SEO Manager</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Re:signal</t>
+          <t>Campions Group</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4473741528/</t>
+          <t>https://www.linkedin.com/jobs/view/4472900894/</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2087,7 +2087,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>United Kingdom (Remote)</t>
+          <t>London Area, United Kingdom (Remote)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -2102,15 +2102,15 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
+          <t>2026-10-07 06:01</t>
         </is>
       </c>
       <c r="J27" s="4" t="n">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>✓ Role: SEO Strategist | ✓ SEO | ✓ Remote | ✓ Fresh</t>
+          <t>✓ Role: SEO Manager | ✓ SEO | ✓ SEO Strategy &amp; Leadership | ✓ Remote</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2123,12 +2123,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior SEO Manager</t>
+          <t>Manager, Search Engine Optimization</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>AutoDS - Automatic Dropshipping Tools</t>
+          <t>Paychex</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4455986307/</t>
+          <t>https://www.linkedin.com/jobs/view/4463924033/</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tel Aviv-Yafo, Tel Aviv District, Israel (Remote)</t>
+          <t>High Point, North Carolina, United States (Remote)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2163,15 +2163,15 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
-        </is>
-      </c>
-      <c r="J28" s="4" t="n">
-        <v>81</v>
+          <t>2026-10-07 06:01</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="n">
+        <v>56</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>✓ Role: SEO Manager | ✓ SEO | ✓ SEO Strategy &amp; Leadership | ✓ Remote | ✓ Fresh</t>
+          <t>✓ Title: search engine optimization | ✓ SEO | ✓ Remote</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2184,12 +2184,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Lead, SEO &amp; Content Strategy</t>
+          <t>SEO &amp; GEO Lead</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Zetexa Global</t>
+          <t>Robert Walters</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4471512635/</t>
+          <t>https://www.linkedin.com/jobs/view/4476390681/</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2209,7 +2209,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Hyderabad, Telangana, India (Remote)</t>
+          <t>Singapore, Singapore (Remote)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2224,15 +2224,15 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
-        </is>
-      </c>
-      <c r="J29" s="3" t="n">
-        <v>59</v>
+          <t>2026-10-07 06:01</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="n">
+        <v>77</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>✓ Title: SEO | ✓ SEO | ✓ Remote | ✓ Fresh</t>
+          <t>✓ Title: SEO | ✓ SEO | ✓ GEO / AI Search | ✓ Remote | ✓ Fresh</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2245,12 +2245,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SEO Lead</t>
+          <t>SEO Lead (w/m/d)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>PhonePe</t>
+          <t>Enpal</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4470827682/</t>
+          <t>https://www.linkedin.com/jobs/view/4467420510/</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bengaluru, Karnataka, India (Remote)</t>
+          <t>Berlin, Germany (Remote)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2285,7 +2285,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
+          <t>2026-10-07 06:01</t>
         </is>
       </c>
       <c r="J30" s="4" t="n">
@@ -2306,12 +2306,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior SEO Manager</t>
+          <t>SEO Account Director</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Got The T-Shirt</t>
+          <t>Starcom</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4473741040/</t>
+          <t>https://www.linkedin.com/jobs/view/4473364093/</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Liverpool, England, United Kingdom (Remote)</t>
+          <t>London, England, United Kingdom (Remote)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2346,15 +2346,15 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
-        </is>
-      </c>
-      <c r="J31" s="4" t="n">
-        <v>81</v>
+          <t>2026-10-07 06:01</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="n">
+        <v>56</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>✓ Role: SEO Manager | ✓ SEO | ✓ SEO Strategy &amp; Leadership | ✓ Remote | ✓ Fresh</t>
+          <t>✓ Title: SEO | ✓ SEO | ✓ Remote</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2367,12 +2367,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SEO Lead at Independent Full-Funnel Marketing Agency</t>
+          <t>Director, SEO/GEO</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Grey Matter Recruitment</t>
+          <t>Fora Travel</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4470882744/</t>
+          <t>https://www.linkedin.com/jobs/view/4454629428/</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>London Area, United Kingdom (Remote)</t>
+          <t>New York, New York, United States (Remote)</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2407,15 +2407,15 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
+          <t>2026-10-07 06:01</t>
         </is>
       </c>
       <c r="J32" s="4" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>✓ Role: SEO Lead | ✓ SEO | ✓ SEO Strategy &amp; Leadership | ✓ Remote | ✓ Fresh</t>
+          <t>✓ Title: SEO | ✓ SEO | ✓ GEO / AI Search | ✓ Remote | ✓ Fresh</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2428,12 +2428,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Director, SEO</t>
+          <t>Head of SEO</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Razorfish</t>
+          <t>LocalEyes Video Production</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4471555256/</t>
+          <t>https://www.linkedin.com/jobs/view/4475158127/</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Chicago, Illinois, United States (Remote)</t>
+          <t>Argentina (Remote)</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2468,15 +2468,15 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
-        </is>
-      </c>
-      <c r="J33" s="3" t="n">
-        <v>59</v>
+          <t>2026-10-07 06:01</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="n">
+        <v>81</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>✓ Title: SEO | ✓ SEO | ✓ Remote | ✓ Fresh</t>
+          <t>✓ Role: Head of SEO | ✓ SEO | ✓ SEO Strategy &amp; Leadership | ✓ Remote | ✓ Fresh</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2489,12 +2489,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Head of SEO</t>
+          <t>Director of SEO &amp; AEO</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>XS.com</t>
+          <t>BizIQ - Smart Growth Marketing</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4471738600/</t>
+          <t>https://www.linkedin.com/jobs/view/4474664500/</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2514,7 +2514,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Limassol, Cyprus (Remote)</t>
+          <t>United States (Remote)</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2529,15 +2529,15 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
+          <t>2026-10-07 06:01</t>
         </is>
       </c>
       <c r="J34" s="4" t="n">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>✓ Role: Head of SEO | ✓ SEO | ✓ SEO Strategy &amp; Leadership | ✓ Remote | ✓ Fresh</t>
+          <t>✓ Title: SEO | ✓ SEO | ✓ GEO / AI Search | ✓ Remote | ✓ Fresh</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2550,12 +2550,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>UK Remote - SEO Lead - Conversion Agency</t>
+          <t>Head of SEO</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Converted</t>
+          <t>LocalEyes Video Production</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4471910089/</t>
+          <t>https://www.linkedin.com/jobs/view/4475135965/</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>United Kingdom (Remote)</t>
+          <t>Brazil (Remote)</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
+          <t>2026-10-07 06:01</t>
         </is>
       </c>
       <c r="J35" s="4" t="n">
@@ -2598,7 +2598,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>✓ Role: SEO Lead | ✓ SEO | ✓ SEO Strategy &amp; Leadership | ✓ Remote | ✓ Fresh</t>
+          <t>✓ Role: Head of SEO | ✓ SEO | ✓ SEO Strategy &amp; Leadership | ✓ Remote | ✓ Fresh</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -2611,12 +2611,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Head of GEO / SEO / Growth Marketing (AI Driven)</t>
+          <t>Director, SEO &amp; AEO</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>MC Group</t>
+          <t>Houzz</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4473217760/</t>
+          <t>https://www.linkedin.com/jobs/view/4439467350/</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2636,7 +2636,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Hong Kong, Hong Kong SAR (Remote)</t>
+          <t>United States (Remote)</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2651,15 +2651,15 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
+          <t>2026-10-07 06:01</t>
         </is>
       </c>
       <c r="J36" s="4" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>✓ Title: SEO | ✓ SEO | ✓ GEO / AI Search | ✓ Remote | ✓ Fresh</t>
+          <t>✓ Title: SEO | ✓ SEO | ✓ GEO / AI Search | ✓ Remote</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -2672,12 +2672,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Head of SEO</t>
+          <t>Head of Client SEO Strategy &amp; Delivery</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Ogooga</t>
+          <t>Digital Executive</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4472735916/</t>
+          <t>https://www.linkedin.com/jobs/view/4472816186/</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bucharest Metropolitan Area (Remote)</t>
+          <t>Colombia (Remote)</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -2712,15 +2712,15 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
-        </is>
-      </c>
-      <c r="J37" s="4" t="n">
-        <v>81</v>
+          <t>2026-10-07 06:01</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="n">
+        <v>68</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>✓ Role: Head of SEO | ✓ SEO | ✓ SEO Strategy &amp; Leadership | ✓ Remote | ✓ Fresh</t>
+          <t>✓ Title: SEO | ✓ SEO | ✓ SEO Strategy &amp; Leadership | ✓ Remote</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -2733,12 +2733,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior SEO Director (Remote)</t>
+          <t>Head of SEO / SEO Lead</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>AllCampus</t>
+          <t>The Adecco Group</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4471724915/</t>
+          <t>https://www.linkedin.com/jobs/view/4472890250/</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2758,7 +2758,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>United States (Remote)</t>
+          <t>Alcobendas, Community of Madrid, Spain (Remote)</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -2773,15 +2773,15 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
-        </is>
-      </c>
-      <c r="J38" s="3" t="n">
-        <v>59</v>
+          <t>2026-10-07 06:01</t>
+        </is>
+      </c>
+      <c r="J38" s="4" t="n">
+        <v>78</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>✓ Title: SEO | ✓ SEO | ✓ Remote | ✓ Fresh</t>
+          <t>✓ Role: SEO Lead | ✓ SEO | ✓ SEO Strategy &amp; Leadership | ✓ Remote</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2794,12 +2794,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SEO HEAD – SaaS/IT</t>
+          <t>VP, SEO Lead - dentsu Media US</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>AIMLEAP</t>
+          <t>dentsu</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4472111773/</t>
+          <t>https://www.linkedin.com/jobs/view/4474640325/</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bengaluru, Karnataka, India (Remote)</t>
+          <t>New York, United States (Remote)</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2834,15 +2834,15 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
-        </is>
-      </c>
-      <c r="J39" s="3" t="n">
-        <v>59</v>
+          <t>2026-10-07 06:01</t>
+        </is>
+      </c>
+      <c r="J39" s="4" t="n">
+        <v>81</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>✓ Title: SEO | ✓ SEO | ✓ Remote | ✓ Fresh</t>
+          <t>✓ Role: SEO Lead | ✓ SEO | ✓ SEO Strategy &amp; Leadership | ✓ Remote | ✓ Fresh</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -2855,12 +2855,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Head of SEO</t>
+          <t>Director of SEO (US Market)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>COLAB PK</t>
+          <t>Pepper</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4473938779/</t>
+          <t>https://www.linkedin.com/jobs/view/4462792199/</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>India (Remote)</t>
+          <t>Mumbai, Maharashtra, India (Remote)</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2895,15 +2895,15 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
-        </is>
-      </c>
-      <c r="J40" s="4" t="n">
-        <v>81</v>
+          <t>2026-10-07 06:01</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="n">
+        <v>56</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>✓ Role: Head of SEO | ✓ SEO | ✓ SEO Strategy &amp; Leadership | ✓ Remote | ✓ Fresh</t>
+          <t>✓ Title: SEO | ✓ SEO | ✓ Remote</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -2916,12 +2916,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Head of SEO and AI Visibility</t>
+          <t>Head of SEO &amp; Growth - Demilked</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Smallpdf</t>
+          <t>Bored Panda Group</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4470852235/</t>
+          <t>https://www.linkedin.com/jobs/view/4474147948/</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>European Economic Area (Remote)</t>
+          <t>Vilnius, Vilniaus, Lithuania (Remote)</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2956,15 +2956,15 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
+          <t>2026-10-07 06:01</t>
         </is>
       </c>
       <c r="J41" s="4" t="n">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>✓ Role: Head of SEO | ✓ SEO | ✓ GEO / AI Search | ✓ SEO Strategy &amp; Leadership | ✓ Remote | ✓ Fresh</t>
+          <t>✓ Role: Head of SEO | ✓ SEO | ✓ SEO Strategy &amp; Leadership | ✓ Remote</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -2977,12 +2977,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Director-SEO_Onsite_New Delhi_10+yrs SEO Exp</t>
+          <t>Director, SEO + AEO</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Techmagnate - A Digital Marketing Agency</t>
+          <t>Tamara Group</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4451784531/</t>
+          <t>https://www.linkedin.com/jobs/view/4465318642/</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3002,7 +3002,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Delhi, India (Remote)</t>
+          <t>Los Angeles Metropolitan Area (Remote)</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -3017,15 +3017,15 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
-        </is>
-      </c>
-      <c r="J42" s="3" t="n">
-        <v>56</v>
+          <t>2026-10-07 06:01</t>
+        </is>
+      </c>
+      <c r="J42" s="4" t="n">
+        <v>74</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>✓ Title: SEO | ✓ SEO | ✓ Remote</t>
+          <t>✓ Title: SEO | ✓ SEO | ✓ GEO / AI Search | ✓ Remote</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3038,12 +3038,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>VP SEO</t>
+          <t>Experience (SEO, GEO) Director</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Stream Companies</t>
+          <t>WPP Media</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4452815763/</t>
+          <t>https://www.linkedin.com/jobs/view/4473699422/</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3063,7 +3063,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>West Chester, Pennsylvania, United States (Remote)</t>
+          <t>Melbourne, Victoria, Australia (Remote)</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -3078,15 +3078,15 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
-        </is>
-      </c>
-      <c r="J43" s="3" t="n">
-        <v>59</v>
+          <t>2026-10-07 06:01</t>
+        </is>
+      </c>
+      <c r="J43" s="4" t="n">
+        <v>77</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>✓ Title: SEO | ✓ SEO | ✓ Remote | ✓ Fresh</t>
+          <t>✓ Title: SEO | ✓ SEO | ✓ GEO / AI Search | ✓ Remote | ✓ Fresh</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3099,12 +3099,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Head of SEO</t>
+          <t>Head of Search &amp; AI Visibility</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Summit Search Group</t>
+          <t>Zoom</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,17 +3114,17 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4473004515/</t>
+          <t>https://www.linkedin.com/jobs/view/4475033755/</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>SEO</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Winnipeg, Manitoba, Canada (Remote)</t>
+          <t>United States (Remote)</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -3139,15 +3139,15 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
-        </is>
-      </c>
-      <c r="J44" s="4" t="n">
-        <v>81</v>
+          <t>2026-10-07 06:01</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>27</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>✓ Role: Head of SEO | ✓ SEO | ✓ SEO Strategy &amp; Leadership | ✓ Remote | ✓ Fresh</t>
+          <t>✓ GEO / AI Search | ✓ Remote</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3160,12 +3160,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Head of SEO &amp; Organic Growth</t>
+          <t>Director - SEO</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>RJA-Consulting</t>
+          <t>TAAS Partners</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4472499865/</t>
+          <t>https://www.linkedin.com/jobs/view/4475151643/</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Manchester Area, United Kingdom (Remote)</t>
+          <t>Bengaluru, Karnataka, India (Remote)</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Job</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3200,15 +3200,15 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
-        </is>
-      </c>
-      <c r="J45" s="4" t="n">
-        <v>81</v>
+          <t>2026-10-07 06:01</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="n">
+        <v>59</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>✓ Role: Head of SEO | ✓ SEO | ✓ SEO Strategy &amp; Leadership | ✓ Remote | ✓ Fresh</t>
+          <t>✓ Title: SEO | ✓ SEO | ✓ Remote | ✓ Fresh</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3221,12 +3221,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SEO Director</t>
+          <t>Director of AEO &amp; SEO</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>BMC Recruitment Group</t>
+          <t>Omniscient Digital</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4473746301/</t>
+          <t>https://www.linkedin.com/jobs/view/4474714326/</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3246,7 +3246,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gateshead, England, United Kingdom (Remote)</t>
+          <t>United States (Remote)</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3261,15 +3261,15 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
-        </is>
-      </c>
-      <c r="J46" s="3" t="n">
-        <v>59</v>
+          <t>2026-10-07 06:01</t>
+        </is>
+      </c>
+      <c r="J46" s="4" t="n">
+        <v>74</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>✓ Title: SEO | ✓ SEO | ✓ Remote | ✓ Fresh</t>
+          <t>✓ Title: SEO | ✓ SEO | ✓ GEO / AI Search | ✓ Remote</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3282,12 +3282,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Head of SEO</t>
+          <t>Director Search Engine Optimization</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SAYCO - Cabinet de recrutement</t>
+          <t>Whizz HR</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4473528779/</t>
+          <t>https://www.linkedin.com/jobs/view/4476544494/</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3307,7 +3307,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lambersart, Hauts-de-France, France (Remote)</t>
+          <t>Bengaluru, Karnataka, India (Remote)</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3322,15 +3322,15 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
-        </is>
-      </c>
-      <c r="J47" s="4" t="n">
-        <v>81</v>
+          <t>2026-10-07 06:01</t>
+        </is>
+      </c>
+      <c r="J47" s="3" t="n">
+        <v>59</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>✓ Role: Head of SEO | ✓ SEO | ✓ SEO Strategy &amp; Leadership | ✓ Remote | ✓ Fresh</t>
+          <t>✓ Title: search engine optimization | ✓ SEO | ✓ Remote | ✓ Fresh</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3343,12 +3343,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SEO Specialist</t>
+          <t>Head Search Engine Optimization</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>big group</t>
+          <t>Saffron Tech Pvt Ltd</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4473211489/</t>
+          <t>https://www.linkedin.com/jobs/view/4474694696/</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Greater London, England, United Kingdom (Remote)</t>
+          <t>South West Delhi, Delhi, India (Remote)</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3383,15 +3383,15 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
-        </is>
-      </c>
-      <c r="J48" s="4" t="n">
-        <v>70</v>
+          <t>2026-10-07 06:01</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="n">
+        <v>59</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>✓ Role: SEO Specialist | ✓ SEO | ✓ Remote | ✓ Fresh</t>
+          <t>✓ Title: search engine optimization | ✓ SEO | ✓ Remote | ✓ Fresh</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3404,12 +3404,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior SEO Specialist</t>
+          <t>Director of SEO - Organic Growth/AI</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>iO</t>
+          <t>AIMLEAP</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4436356705/</t>
+          <t>https://www.linkedin.com/jobs/view/4474226845/</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3429,7 +3429,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Den Bosch, North Brabant, Netherlands (Remote)</t>
+          <t>Bengaluru, Karnataka, India (Remote)</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3444,15 +3444,15 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
+          <t>2026-10-07 06:01</t>
         </is>
       </c>
       <c r="J49" s="3" t="n">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>✓ Role: SEO Specialist | ✓ SEO | ✓ Remote</t>
+          <t>✓ Title: SEO | ✓ SEO | ✓ Remote | ✓ Fresh</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3465,12 +3465,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior SEO Specialist</t>
+          <t>Senior SEO &amp; LLMO Executive</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>iO</t>
+          <t>M+C Saatchi Group</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4436361618/</t>
+          <t>https://www.linkedin.com/jobs/view/4465806164/</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3490,7 +3490,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Utrecht, Utrecht, Netherlands (Remote)</t>
+          <t>Jakarta Metropolitan Area (Remote)</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3505,15 +3505,15 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
+          <t>2026-10-07 06:01</t>
         </is>
       </c>
       <c r="J50" s="3" t="n">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>✓ Role: SEO Specialist | ✓ SEO | ✓ Remote</t>
+          <t>✓ Title: SEO | ✓ SEO | ✓ Remote</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3526,12 +3526,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior SEO Specialist</t>
+          <t>Senior Organic Performance (SEO) Executive</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>M3aarf منصة معارف</t>
+          <t>ROAST</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4470821358/</t>
+          <t>https://www.linkedin.com/jobs/view/4464349339/</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Giza, Al Jizah, Egypt (Remote)</t>
+          <t>London Area, United Kingdom (Remote)</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3566,15 +3566,15 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
+          <t>2026-10-07 06:01</t>
         </is>
       </c>
       <c r="J51" s="3" t="n">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>✓ Role: SEO Specialist | ✓ SEO | ✓ Remote</t>
+          <t>✓ Title: SEO | ✓ SEO | ✓ Remote</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -3587,12 +3587,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior SEO Specialist</t>
+          <t>SEO Specialist (News Media, Technical &amp; AI Search)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Cedar Global Solutions</t>
+          <t>HT Digital Streams</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4471924791/</t>
+          <t>https://www.linkedin.com/jobs/view/4474140631/</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lahore, Punjab, Pakistan (Remote)</t>
+          <t>Delhi, India (Remote)</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3627,15 +3627,15 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
+          <t>2026-10-07 06:01</t>
         </is>
       </c>
       <c r="J52" s="4" t="n">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>✓ Role: SEO Specialist | ✓ SEO | ✓ Remote | ✓ Fresh</t>
+          <t>✓ Role: SEO Specialist | ✓ SEO | ✓ GEO / AI Search | ✓ Remote</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3648,12 +3648,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior/SEO &amp; GEO Strategist</t>
+          <t>Senior SEO Specialist</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>OOm Singapore</t>
+          <t>Liberty Marketing</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4472478901/</t>
+          <t>https://www.linkedin.com/jobs/view/4474710657/</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3673,7 +3673,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Singapore, Singapore (Remote)</t>
+          <t>United Kingdom (Remote)</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3688,15 +3688,15 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
-        </is>
-      </c>
-      <c r="J53" s="4" t="n">
-        <v>77</v>
+          <t>2026-10-07 06:01</t>
+        </is>
+      </c>
+      <c r="J53" s="3" t="n">
+        <v>67</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>✓ Title: SEO | ✓ SEO | ✓ GEO / AI Search | ✓ Remote | ✓ Fresh</t>
+          <t>✓ Role: SEO Specialist | ✓ SEO | ✓ Remote</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3709,12 +3709,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior SEO Specialist (SEO + GEO)</t>
+          <t>Senior Technical SEO Specialist</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Jobgether</t>
+          <t>TAL Agency</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4471336894/</t>
+          <t>https://www.linkedin.com/jobs/view/4476186185/</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3734,7 +3734,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Italy (Remote)</t>
+          <t>Bolton, England, United Kingdom (Remote)</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3749,15 +3749,15 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
+          <t>2026-10-07 06:01</t>
         </is>
       </c>
       <c r="J54" s="4" t="n">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>✓ Role: SEO Specialist | ✓ SEO | ✓ GEO / AI Search | ✓ Remote | ✓ Fresh</t>
+          <t>✓ Role: SEO Specialist | ✓ SEO | ✓ Technical &amp; On-page | ✓ Remote | ✓ Fresh</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -3770,12 +3770,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SEO &amp; AEO Specialist</t>
+          <t>Expert SEO / GEO</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Mondiad</t>
+          <t>T&amp;S (Technology &amp; Strategy)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4452850340/</t>
+          <t>https://www.linkedin.com/jobs/view/4473655870/</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -3795,7 +3795,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Bucharest, Romania (Remote)</t>
+          <t>Greater Paris Metropolitan Region (Remote)</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3810,15 +3810,15 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
+          <t>2026-10-07 06:01</t>
         </is>
       </c>
       <c r="J55" s="4" t="n">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>✓ Role: AEO Specialist | ✓ SEO | ✓ GEO / AI Search | ✓ Remote | ✓ Fresh</t>
+          <t>✓ Title: SEO | ✓ SEO | ✓ GEO / AI Search | ✓ Remote | ✓ Fresh</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -3831,12 +3831,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior SEO-specialist inom AI-sök och organisk synlighet</t>
+          <t>SEO Lead</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Boostr.se</t>
+          <t>Dr Lal PathLabs</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4472158262/</t>
+          <t>https://www.linkedin.com/jobs/view/4476552141/</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Jönköping, Jönköping County, Sweden (Remote)</t>
+          <t>Gurugram, Haryana, India (Remote)</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -3871,15 +3871,15 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
+          <t>2026-10-07 06:01</t>
         </is>
       </c>
       <c r="J56" s="4" t="n">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>✓ Role: SEO Specialist | ✓ SEO | ✓ Remote | ✓ Fresh</t>
+          <t>✓ Role: SEO Lead | ✓ SEO | ✓ SEO Strategy &amp; Leadership | ✓ Remote | ✓ Fresh</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -3892,12 +3892,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior SEO Consultant cum strategist</t>
+          <t>Senior Search Engine Optimization</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Expansion Desk</t>
+          <t>Maraki</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4472672640/</t>
+          <t>https://www.linkedin.com/jobs/view/4475544968/</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3917,12 +3917,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mumbai, Maharashtra, India (Remote)</t>
+          <t>Cairo, Egypt (Remote)</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Job</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3932,15 +3932,15 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
-        </is>
-      </c>
-      <c r="J57" s="4" t="n">
-        <v>70</v>
+          <t>2026-10-07 06:01</t>
+        </is>
+      </c>
+      <c r="J57" s="3" t="n">
+        <v>59</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>✓ Role: SEO Consultant | ✓ SEO | ✓ Remote | ✓ Fresh</t>
+          <t>✓ Title: search engine optimization | ✓ SEO | ✓ Remote | ✓ Fresh</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -3953,12 +3953,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior SEO Specialist - TJ / 1890385</t>
+          <t>SEO Specialist - SE England</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Recruit AI</t>
+          <t>Jump IT Recruitment Solutions Limited</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4473936083/</t>
+          <t>https://www.linkedin.com/jobs/view/4476179033/</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3978,7 +3978,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lahore, Punjab, Pakistan (Remote)</t>
+          <t>London Area, United Kingdom (Remote)</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
+          <t>2026-10-07 06:01</t>
         </is>
       </c>
       <c r="J58" s="4" t="n">
@@ -4014,12 +4014,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>SEO/AEO/GEO Senior Strategist (Agency Experience Must)</t>
+          <t>CDI Consultant (e) Senior SEO H/F-Toulouse</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Growth Hackers</t>
+          <t>PIXALIONE | SEO, PAID, IA, DATA &amp; CRO</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4472166371/</t>
+          <t>https://www.linkedin.com/jobs/view/4474309498/</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4039,12 +4039,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Bengaluru, Karnataka, India (Remote)</t>
+          <t>Toulouse, Occitanie, France (Remote)</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Job</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4054,15 +4054,15 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
-        </is>
-      </c>
-      <c r="J59" s="4" t="n">
-        <v>80</v>
+          <t>2026-10-07 06:01</t>
+        </is>
+      </c>
+      <c r="J59" s="3" t="n">
+        <v>56</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>✓ Title: SEO | ✓ SEO | ✓ GEO / AI Search | ✓ Remote | ✓ Fresh</t>
+          <t>✓ Title: SEO | ✓ SEO | ✓ Remote</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4075,12 +4075,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior SEO Stratege (m/w/d)</t>
+          <t>Senior SEO Specialist</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>HeizungsDiscount24 GmbH</t>
+          <t>Brandsolute™</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -4090,7 +4090,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4471266263/</t>
+          <t>https://www.linkedin.com/jobs/view/4474901268/</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Gießen, Hesse, Germany (Remote)</t>
+          <t>Colombo, Western Province, Sri Lanka (Remote)</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -4115,15 +4115,15 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
-        </is>
-      </c>
-      <c r="J60" s="3" t="n">
-        <v>59</v>
+          <t>2026-10-07 06:01</t>
+        </is>
+      </c>
+      <c r="J60" s="4" t="n">
+        <v>70</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>✓ Title: SEO | ✓ SEO | ✓ Remote | ✓ Fresh</t>
+          <t>✓ Role: SEO Specialist | ✓ SEO | ✓ Remote | ✓ Fresh</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4136,12 +4136,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>SEO Manager</t>
+          <t>Seo Specialist</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>DesignRush</t>
+          <t>JUMPPEAK</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -4151,7 +4151,7 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4473503415/</t>
+          <t>https://www.linkedin.com/jobs/view/4476171654/</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Belgrade, Serbia (Remote)</t>
+          <t>Qesm El Sheikh Zaid, Al Jizah, Egypt (Remote)</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -4176,15 +4176,15 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
+          <t>2026-10-07 06:01</t>
         </is>
       </c>
       <c r="J61" s="4" t="n">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>✓ Role: SEO Manager | ✓ SEO | ✓ SEO Strategy &amp; Leadership | ✓ Remote | ✓ Fresh</t>
+          <t>✓ Role: SEO Specialist | ✓ SEO | ✓ Remote | ✓ Fresh</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4197,12 +4197,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>SEO Manager</t>
+          <t>CDI - Consultant(e) Senior SEO H/F</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Revpanda Group</t>
+          <t>PIXALIONE | SEO, PAID, IA, DATA &amp; CRO</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -4212,7 +4212,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4460605090/</t>
+          <t>https://www.linkedin.com/jobs/view/4475544592/</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -4222,12 +4222,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>European Union (Remote)</t>
+          <t>Paris, Île-de-France, France (Remote)</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Job</t>
+          <t>Consulting</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -4237,15 +4237,15 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
-        </is>
-      </c>
-      <c r="J62" s="4" t="n">
-        <v>81</v>
+          <t>2026-10-07 06:01</t>
+        </is>
+      </c>
+      <c r="J62" s="3" t="n">
+        <v>59</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>✓ Role: SEO Manager | ✓ SEO | ✓ SEO Strategy &amp; Leadership | ✓ Remote | ✓ Fresh</t>
+          <t>✓ Title: SEO | ✓ SEO | ✓ Remote | ✓ Fresh</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4258,12 +4258,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SEO (Search Engine Optimization) Manager (Remote, Columbus)</t>
+          <t>Search Engine Optimization Specialist</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Blacksmith Agency</t>
+          <t>VelivoHR</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4472782099/</t>
+          <t>https://www.linkedin.com/jobs/view/4475525871/</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4283,7 +4283,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>United States (Remote)</t>
+          <t>Mumbai Metropolitan Region (Remote)</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -4298,15 +4298,15 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
+          <t>2026-10-07 06:01</t>
         </is>
       </c>
       <c r="J63" s="3" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>✓ Title: SEO | ✓ SEO | ✓ Remote | ✓ Fresh</t>
+          <t>✓ Title: search engine optimization | ✓ SEO | ✓ Remote | ✓ Fresh</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -4319,12 +4319,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Manager – SEO</t>
+          <t>Group Senior SEO Specialist</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>GEP Worldwide</t>
+          <t>FEG</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -4334,7 +4334,7 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4471925342/</t>
+          <t>https://www.linkedin.com/jobs/view/4456237497/</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4344,7 +4344,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Navi Mumbai, Maharashtra, India (Remote)</t>
+          <t>Prague, Czechia (Remote)</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -4359,15 +4359,15 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
-        </is>
-      </c>
-      <c r="J64" s="3" t="n">
-        <v>59</v>
+          <t>2026-10-07 06:01</t>
+        </is>
+      </c>
+      <c r="J64" s="4" t="n">
+        <v>70</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>✓ Title: SEO | ✓ SEO | ✓ Remote | ✓ Fresh</t>
+          <t>✓ Role: SEO Specialist | ✓ SEO | ✓ Remote | ✓ Fresh</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -4380,12 +4380,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>SEO Manager</t>
+          <t>SEO Manager - Luxury - Up to £55,000</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>QHT Clinic</t>
+          <t>Blu Digital</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4395,7 +4395,7 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4472328139/</t>
+          <t>https://www.linkedin.com/jobs/view/4473648219/</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4405,7 +4405,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rohini, Delhi, India (Remote)</t>
+          <t>London Area, United Kingdom (Remote)</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -4420,7 +4420,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
+          <t>2026-10-07 06:01</t>
         </is>
       </c>
       <c r="J65" s="4" t="n">
@@ -4441,12 +4441,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>SEO (Search Engine Optimization) Manager (Remote, San Diego)</t>
+          <t>SEO Manager</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Blacksmith Agency</t>
+          <t>DesignRush</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -4456,7 +4456,7 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4473297485/</t>
+          <t>https://www.linkedin.com/jobs/view/4472022939/</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>United States (Remote)</t>
+          <t>Serbia (Remote)</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -4481,15 +4481,15 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
-        </is>
-      </c>
-      <c r="J66" s="3" t="n">
-        <v>63</v>
+          <t>2026-10-07 06:01</t>
+        </is>
+      </c>
+      <c r="J66" s="4" t="n">
+        <v>81</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>✓ Title: SEO | ✓ SEO | ✓ Remote | ✓ Fresh</t>
+          <t>✓ Role: SEO Manager | ✓ SEO | ✓ SEO Strategy &amp; Leadership | ✓ Remote | ✓ Fresh</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4502,12 +4502,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Organic Search &amp; SEO Manager</t>
+          <t>SEO Manager (m/w/d)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>LaSalle Network</t>
+          <t>11880.com</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -4517,7 +4517,7 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4473265614/</t>
+          <t>https://www.linkedin.com/jobs/view/4474570794/</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Chicago, Illinois, United States (Remote)</t>
+          <t>Cologne, North Rhine-Westphalia, Germany (Remote)</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -4542,15 +4542,15 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
+          <t>2026-10-07 06:01</t>
         </is>
       </c>
       <c r="J67" s="4" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>✓ Role: SEO Manager | ✓ SEO | ✓ SEO Strategy &amp; Leadership | ✓ Remote | ✓ Fresh</t>
+          <t>✓ Role: SEO Manager | ✓ SEO | ✓ SEO Strategy &amp; Leadership | ✓ Remote</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -4563,12 +4563,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>SEO Performance Manager</t>
+          <t>SEO &amp; AI Search Manager (w/m/d)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Paradise Media</t>
+          <t>LAUDO</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4578,7 +4578,7 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4462968694/</t>
+          <t>https://www.linkedin.com/jobs/view/4473150159/</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -4588,7 +4588,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Saint Julian's, Malta (Remote)</t>
+          <t>Berlin, Berlin, Germany (Remote)</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -4603,15 +4603,15 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
-        </is>
-      </c>
-      <c r="J68" s="3" t="n">
-        <v>59</v>
+          <t>2026-10-07 06:01</t>
+        </is>
+      </c>
+      <c r="J68" s="4" t="n">
+        <v>74</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>✓ Title: SEO | ✓ SEO | ✓ Remote | ✓ Fresh</t>
+          <t>✓ Title: SEO | ✓ SEO | ✓ GEO / AI Search | ✓ Remote</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -4624,12 +4624,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Manager - SEO</t>
+          <t>Marketing Manager SEO, AWS Search Marketing</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Performics India</t>
+          <t>Amazon Web Services (AWS)</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -4639,7 +4639,7 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4473778704/</t>
+          <t>https://www.linkedin.com/jobs/view/4474793819/</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4649,7 +4649,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mumbai, Maharashtra, India (Remote)</t>
+          <t>New York, United States (Remote)</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -4664,15 +4664,15 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
-        </is>
-      </c>
-      <c r="J69" s="3" t="n">
-        <v>59</v>
+          <t>2026-10-07 06:01</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>0</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>✓ Title: SEO | ✓ SEO | ✓ Remote | ✓ Fresh</t>
+          <t>✗ Excluded: marketing manager</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -4690,7 +4690,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Suntransfers</t>
+          <t>Platin Gaming Ltd.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4700,7 +4700,7 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4472703450/</t>
+          <t>https://www.linkedin.com/jobs/view/4473858405/</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4710,7 +4710,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Barcelona, Catalonia, Spain (Remote)</t>
+          <t>Malta (Remote)</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -4725,15 +4725,15 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
+          <t>2026-10-07 06:01</t>
         </is>
       </c>
       <c r="J70" s="4" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>✓ Role: SEO Manager | ✓ SEO | ✓ SEO Strategy &amp; Leadership | ✓ Remote | ✓ Fresh</t>
+          <t>✓ Role: SEO Manager | ✓ SEO | ✓ SEO Strategy &amp; Leadership | ✓ Remote</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -4751,7 +4751,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>RedCat Digital</t>
+          <t>Silverback Strategies</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4472447541/</t>
+          <t>https://www.linkedin.com/jobs/view/4475034466/</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4771,7 +4771,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Woking, England, United Kingdom (Remote)</t>
+          <t>United States (Remote)</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -4786,7 +4786,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
+          <t>2026-10-07 06:01</t>
         </is>
       </c>
       <c r="J71" s="4" t="n">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Nasdaq</t>
+          <t>Cactus Communications</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4446142662/</t>
+          <t>https://www.linkedin.com/jobs/view/4475149253/</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Atlanta, Georgia, United States (Remote)</t>
+          <t>Mumbai, Maharashtra, India (Remote)</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -4847,7 +4847,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
+          <t>2026-10-07 06:01</t>
         </is>
       </c>
       <c r="J72" s="4" t="n">
@@ -4868,12 +4868,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Search Engine Optimization (SEO) Manager</t>
+          <t>Senior SEO Manager</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Palo Alto Networks</t>
+          <t>Konker</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4883,7 +4883,7 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4432714675/</t>
+          <t>https://www.linkedin.com/jobs/view/4476180055/</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4893,7 +4893,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Santa Clara, California, United States (Remote)</t>
+          <t>West Sussex, England, United Kingdom (Remote)</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -4908,15 +4908,15 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
-        </is>
-      </c>
-      <c r="J73" s="3" t="n">
-        <v>60</v>
+          <t>2026-10-07 06:01</t>
+        </is>
+      </c>
+      <c r="J73" s="4" t="n">
+        <v>81</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>✓ Title: SEO | ✓ SEO | ✓ Remote</t>
+          <t>✓ Role: SEO Manager | ✓ SEO | ✓ SEO Strategy &amp; Leadership | ✓ Remote | ✓ Fresh</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -4929,12 +4929,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Search Engine Optimization Manager (SEO Manager)</t>
+          <t>SEO (Search Engine Optimization) Manager (Remote, Boston)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Fenzo Digital</t>
+          <t>Blacksmith Agency</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4471973141/</t>
+          <t>https://www.linkedin.com/jobs/view/4475008051/</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -4954,7 +4954,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Pune/Pimpri-Chinchwad Area (Remote)</t>
+          <t>United States (Remote)</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -4969,15 +4969,15 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
-        </is>
-      </c>
-      <c r="J74" s="4" t="n">
-        <v>81</v>
+          <t>2026-10-07 06:01</t>
+        </is>
+      </c>
+      <c r="J74" s="3" t="n">
+        <v>60</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>✓ Role: SEO Manager | ✓ SEO | ✓ SEO Strategy &amp; Leadership | ✓ Remote | ✓ Fresh</t>
+          <t>✓ Title: SEO | ✓ SEO | ✓ Remote</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -4990,12 +4990,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Search Engine Optimization Manager (SEO Manager)</t>
+          <t>Growth SEO Manager</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Fenzo Digital</t>
+          <t>Muzz</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -5005,7 +5005,7 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4471974229/</t>
+          <t>https://www.linkedin.com/jobs/view/4472563278/</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -5015,7 +5015,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Greater Delhi Area (Remote)</t>
+          <t>London Area, United Kingdom (Remote)</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -5030,15 +5030,15 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
+          <t>2026-10-07 06:01</t>
         </is>
       </c>
       <c r="J75" s="4" t="n">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>✓ Role: SEO Manager | ✓ SEO | ✓ SEO Strategy &amp; Leadership | ✓ Remote | ✓ Fresh</t>
+          <t>✓ Role: SEO Manager | ✓ SEO | ✓ SEO Strategy &amp; Leadership | ✓ Remote</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5051,12 +5051,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>SEO/GEO Manager</t>
+          <t>SEO (Search Engine Optimization) Manager (Remote, Detroit)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Harper</t>
+          <t>Blacksmith Agency</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -5066,7 +5066,7 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4473560273/</t>
+          <t>https://www.linkedin.com/jobs/view/4475509316/</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>New York, New York, United States (Remote)</t>
+          <t>United States (Remote)</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -5091,15 +5091,15 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
-        </is>
-      </c>
-      <c r="J76" s="4" t="n">
-        <v>77</v>
+          <t>2026-10-07 06:01</t>
+        </is>
+      </c>
+      <c r="J76" s="3" t="n">
+        <v>63</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>✓ Title: SEO | ✓ SEO | ✓ GEO / AI Search | ✓ Remote | ✓ Fresh</t>
+          <t>✓ Title: SEO | ✓ SEO | ✓ Remote | ✓ Fresh</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -5112,12 +5112,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior SEO Executive</t>
+          <t>SEO and Organic Search Manager</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Frasers Group</t>
+          <t>CEEK Marketing</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -5127,7 +5127,7 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4471707994/</t>
+          <t>https://www.linkedin.com/jobs/view/4476172726/</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5137,7 +5137,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Shirebrook, England, United Kingdom (Remote)</t>
+          <t>London, England, United Kingdom (Remote)</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -5152,7 +5152,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
+          <t>2026-10-07 06:01</t>
         </is>
       </c>
       <c r="J77" s="3" t="n">
@@ -5173,12 +5173,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Spécialiste SEO/GEO et découvrabilité</t>
+          <t>SEO Manager</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>REF Digital</t>
+          <t>dentsu</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -5188,7 +5188,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4473920040/</t>
+          <t>https://www.linkedin.com/jobs/view/4473365296/</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Montreal, Quebec, Canada (Remote)</t>
+          <t>Dublin, County Dublin, Ireland (Remote)</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -5213,15 +5213,15 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
+          <t>2026-10-07 06:01</t>
         </is>
       </c>
       <c r="J78" s="4" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>✓ Title: SEO | ✓ SEO | ✓ GEO / AI Search | ✓ Remote | ✓ Fresh</t>
+          <t>✓ Role: SEO Manager | ✓ SEO | ✓ SEO Strategy &amp; Leadership | ✓ Remote</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -5234,12 +5234,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>SEO Executive</t>
+          <t>Organic Search &amp; SEO Manager</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Searchability®</t>
+          <t>LaSalle Network</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -5249,7 +5249,7 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4472477265/</t>
+          <t>https://www.linkedin.com/jobs/view/4475841424/</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Sydney, New South Wales, Australia (Remote)</t>
+          <t>Cleveland, Ohio, United States (Remote)</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -5274,15 +5274,15 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
-        </is>
-      </c>
-      <c r="J79" s="3" t="n">
-        <v>56</v>
+          <t>2026-10-07 06:01</t>
+        </is>
+      </c>
+      <c r="J79" s="4" t="n">
+        <v>81</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>✓ Title: SEO | ✓ SEO | ✓ Remote</t>
+          <t>✓ Role: SEO Manager | ✓ SEO | ✓ SEO Strategy &amp; Leadership | ✓ Remote | ✓ Fresh</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -5295,12 +5295,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>MŁODSZY SPECJALISTA DS. SEO</t>
+          <t>SEO Manager | THG Beauty</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Result Media. Performance. Digital. Experts</t>
+          <t>THG</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5310,7 +5310,7 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4472771705/</t>
+          <t>https://www.linkedin.com/jobs/view/4467085624/</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -5320,7 +5320,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Warsaw, Mazowieckie, Poland (Remote)</t>
+          <t>Manchester, England, United Kingdom (Remote)</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -5335,15 +5335,15 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
-        </is>
-      </c>
-      <c r="J80" s="3" t="n">
-        <v>59</v>
+          <t>2026-10-07 06:01</t>
+        </is>
+      </c>
+      <c r="J80" s="4" t="n">
+        <v>81</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>✓ Title: SEO | ✓ SEO | ✓ Remote | ✓ Fresh</t>
+          <t>✓ Role: SEO Manager | ✓ SEO | ✓ SEO Strategy &amp; Leadership | ✓ Remote | ✓ Fresh</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -5356,12 +5356,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>AEO/SEO Executive</t>
+          <t>Manager, Search Engine Optimization</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>ReraTracker</t>
+          <t>Paychex</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -5371,7 +5371,7 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4471914027/</t>
+          <t>https://www.linkedin.com/jobs/view/4463916505/</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Noida, Uttar Pradesh, India (Remote)</t>
+          <t>Sarasota, Florida, United States (Remote)</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -5396,15 +5396,15 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
-        </is>
-      </c>
-      <c r="J81" s="4" t="n">
-        <v>77</v>
+          <t>2026-10-07 06:01</t>
+        </is>
+      </c>
+      <c r="J81" s="3" t="n">
+        <v>56</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>✓ Title: SEO | ✓ SEO | ✓ GEO / AI Search | ✓ Remote | ✓ Fresh</t>
+          <t>✓ Title: search engine optimization | ✓ SEO | ✓ Remote</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -5417,12 +5417,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>SEO Executive (1 year) On-site</t>
+          <t>Manager, Search Engine Optimization</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SprigStack | Software Development Company</t>
+          <t>Paychex</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -5432,7 +5432,7 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4472126540/</t>
+          <t>https://www.linkedin.com/jobs/view/4463925032/</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -5442,7 +5442,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ahmedabad, Gujarat, India (Remote)</t>
+          <t>West Palm Beach, Florida, United States (Remote)</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -5457,15 +5457,15 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
+          <t>2026-10-07 06:01</t>
         </is>
       </c>
       <c r="J82" s="3" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>✓ Title: SEO | ✓ SEO | ✓ Remote | ✓ Fresh</t>
+          <t>✓ Title: search engine optimization | ✓ SEO | ✓ Remote</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -5478,12 +5478,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Search Engine Optimization Specialist</t>
+          <t>Senior Content &amp; SEO Marketing Manager</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Silicon Hub Pvt. Ltd.</t>
+          <t>Focus Partners</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5493,7 +5493,7 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4473722843/</t>
+          <t>https://www.linkedin.com/jobs/view/4456734112/</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -5503,7 +5503,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kathmandu, Bāgmatī, Nepal (Remote)</t>
+          <t>Wacker, South Dakota, United States (Remote)</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -5518,15 +5518,15 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
-        </is>
-      </c>
-      <c r="J83" s="3" t="n">
-        <v>59</v>
+          <t>2026-10-07 06:01</t>
+        </is>
+      </c>
+      <c r="J83" t="n">
+        <v>0</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>✓ Title: search engine optimization | ✓ SEO | ✓ Remote | ✓ Fresh</t>
+          <t>✗ Excluded: marketing manager</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -5539,12 +5539,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior SEO Specialist (SEO + GEO)</t>
+          <t>SEO Manager</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Jobgether</t>
+          <t>Stagwell Media</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5554,7 +5554,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4471336903/</t>
+          <t>https://www.linkedin.com/jobs/view/4448653470/</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5564,12 +5564,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Germany (Remote)</t>
+          <t>London, England, United Kingdom (Remote)</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Job</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -5579,15 +5579,15 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
+          <t>2026-10-07 06:01</t>
         </is>
       </c>
       <c r="J84" s="4" t="n">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>✓ Role: SEO Specialist | ✓ SEO | ✓ GEO / AI Search | ✓ SEO Strategy &amp; Leadership | ✓ Technical &amp; On-page | ✓ Off-page &amp; Link Building | ✓ Search Console &amp; Analytics | ✓ Keyword Research | ✓ Remote | ✓ Fresh</t>
+          <t>✓ Role: SEO Manager | ✓ SEO | ✓ SEO Strategy &amp; Leadership | ✓ Remote | ✓ Fresh</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -5600,12 +5600,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior SEO Specialist (SEO + GEO)</t>
+          <t>Search Engine Optimization Manager</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Jobgether</t>
+          <t>Omni Studio</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4471343492/</t>
+          <t>https://www.linkedin.com/jobs/view/4454293635/</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Netherlands (Remote)</t>
+          <t>Nashik, Maharashtra, India (Remote)</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Job</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5640,15 +5640,15 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
-        </is>
-      </c>
-      <c r="J85" s="4" t="n">
-        <v>91</v>
+          <t>2026-10-07 06:01</t>
+        </is>
+      </c>
+      <c r="J85" s="3" t="n">
+        <v>59</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>✓ Role: SEO Specialist | ✓ SEO | ✓ GEO / AI Search | ✓ SEO Strategy &amp; Leadership | ✓ Technical &amp; On-page | ✓ Off-page &amp; Link Building | ✓ Search Console &amp; Analytics | ✓ Keyword Research | ✓ Remote | ✓ Fresh</t>
+          <t>✓ Title: search engine optimization | ✓ SEO | ✓ Remote | ✓ Fresh</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -5661,12 +5661,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Search Engine Optimization Specialist</t>
+          <t>SEO Manager (German-speaking)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>mangoDigital</t>
+          <t>fonio.ai</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4472183081/</t>
+          <t>https://www.linkedin.com/jobs/view/4476303486/</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5686,7 +5686,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>New Delhi, Delhi, India (Remote)</t>
+          <t>Munich, Bavaria, Germany (Remote)</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -5701,15 +5701,15 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
-        </is>
-      </c>
-      <c r="J86" s="3" t="n">
-        <v>64</v>
+          <t>2026-10-07 06:01</t>
+        </is>
+      </c>
+      <c r="J86" s="4" t="n">
+        <v>81</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>✓ Title: search engine optimization | ✓ SEO | ✓ Remote | ✓ Fresh</t>
+          <t>✓ Role: SEO Manager | ✓ SEO | ✓ SEO Strategy &amp; Leadership | ✓ Remote | ✓ Fresh</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -5722,12 +5722,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>SEO Executive</t>
+          <t>Search Engine Optimization Manager</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>TEKNIKA SOLUTIONS</t>
+          <t>eSEO Solutions : Digital Marketing Agency</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -5737,7 +5737,7 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4471320673/</t>
+          <t>https://www.linkedin.com/jobs/view/4474671735/</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5747,12 +5747,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Trivandrum, Kerala, India (Remote)</t>
+          <t>Gurugram, Haryana, India (Remote)</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Job</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5762,15 +5762,15 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
-        </is>
-      </c>
-      <c r="J87" s="4" t="n">
-        <v>81</v>
+          <t>2026-10-07 06:01</t>
+        </is>
+      </c>
+      <c r="J87" s="3" t="n">
+        <v>59</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>✓ Title: SEO | ✓ SEO | ✓ Technical &amp; On-page | ✓ Off-page &amp; Link Building | ✓ Search Console &amp; Analytics | ✓ Keyword Research | ✓ Remote | ✓ Fresh</t>
+          <t>✓ Title: search engine optimization | ✓ SEO | ✓ Remote | ✓ Fresh</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -5783,12 +5783,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>SEO Executive</t>
+          <t>Specialista SEO</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>iRoid Solutions</t>
+          <t>MM ONE Group Srl</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -5798,7 +5798,7 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4471716670/</t>
+          <t>https://www.linkedin.com/jobs/view/4468541798/</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5808,7 +5808,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Surat, Gujarat, India (Remote)</t>
+          <t>Noventa di Piave, Veneto, Italy (Remote)</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -5823,15 +5823,15 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
-        </is>
-      </c>
-      <c r="J88" s="4" t="n">
-        <v>80</v>
+          <t>2026-10-07 06:01</t>
+        </is>
+      </c>
+      <c r="J88" s="3" t="n">
+        <v>59</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>✓ Title: SEO | ✓ SEO | ✓ Technical &amp; On-page | ✓ Search Console &amp; Analytics | ✓ Keyword Research | ✓ Remote | ✓ Fresh</t>
+          <t>✓ Title: SEO | ✓ SEO | ✓ Remote | ✓ Fresh</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -5849,7 +5849,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Selfcraft Media</t>
+          <t>MAVIP</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4471286019/</t>
+          <t>https://www.linkedin.com/jobs/view/4473838971/</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5869,12 +5869,12 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rajkot, Gujarat, India (Remote)</t>
+          <t>Indore, Madhya Pradesh, India (Remote)</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Job</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -5884,15 +5884,15 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
-        </is>
-      </c>
-      <c r="J89" s="4" t="n">
-        <v>91</v>
+          <t>2026-10-07 06:01</t>
+        </is>
+      </c>
+      <c r="J89" s="3" t="n">
+        <v>56</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>✓ Title: search engine optimization | ✓ SEO | ✓ GEO / AI Search | ✓ Technical &amp; On-page | ✓ Off-page &amp; Link Building | ✓ Search Console &amp; Analytics | ✓ Keyword Research | ✓ WordPress / Ecommerce SEO | ✓ Remote | ✓ Fresh</t>
+          <t>✓ Title: search engine optimization | ✓ SEO | ✓ Remote</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -5905,12 +5905,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior SEO Specialist</t>
+          <t>Senior Seo Executive</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Proleaders Company - شركة نخبة القادة</t>
+          <t>Digital House</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -5920,7 +5920,7 @@
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4473907615/</t>
+          <t>https://www.linkedin.com/jobs/view/4475599625/</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Giza, Al Jizah, Egypt (Remote)</t>
+          <t>Istanbul, Türkiye (Remote)</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -5945,15 +5945,15 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
-        </is>
-      </c>
-      <c r="J90" s="4" t="n">
-        <v>91</v>
+          <t>2026-10-07 06:01</t>
+        </is>
+      </c>
+      <c r="J90" s="3" t="n">
+        <v>59</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>✓ Role: SEO Specialist | ✓ SEO | ✓ Technical &amp; On-page | ✓ Off-page &amp; Link Building | ✓ Search Console &amp; Analytics | ✓ Keyword Research | ✓ Remote | ✓ Fresh</t>
+          <t>✓ Title: SEO | ✓ SEO | ✓ Remote | ✓ Fresh</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -5966,12 +5966,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>SEO Executive</t>
+          <t>Seo Specialist</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>JobTrade</t>
+          <t>PGS TILE MART</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -5981,7 +5981,7 @@
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4471592333/</t>
+          <t>https://www.linkedin.com/jobs/view/4473840827/</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -5991,7 +5991,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Gurugram, Haryana, India (Remote)</t>
+          <t>Greater Madurai Area (Remote)</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -6006,15 +6006,15 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
-        </is>
-      </c>
-      <c r="J91" s="4" t="n">
-        <v>81</v>
+          <t>2026-10-07 06:01</t>
+        </is>
+      </c>
+      <c r="J91" s="3" t="n">
+        <v>67</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>✓ Title: SEO | ✓ SEO | ✓ Technical &amp; On-page | ✓ Off-page &amp; Link Building | ✓ Search Console &amp; Analytics | ✓ Keyword Research | ✓ Remote | ✓ Fresh</t>
+          <t>✓ Role: SEO Specialist | ✓ SEO | ✓ Remote</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -6027,12 +6027,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>SEO Executive</t>
+          <t>Senior SEO &amp; GEO Specialist</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Seven Seas Digital Marketing Agency</t>
+          <t>Grupo Acerca</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -6042,7 +6042,7 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4473520323/</t>
+          <t>https://www.linkedin.com/jobs/view/4472932146/</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -6052,7 +6052,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Pune Division, Maharashtra, India (Remote)</t>
+          <t>Tomares, Andalusia, Spain (Remote)</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -6067,7 +6067,7 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
+          <t>2026-10-07 06:01</t>
         </is>
       </c>
       <c r="J92" s="4" t="n">
@@ -6075,7 +6075,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>✓ Title: SEO | ✓ SEO | ✓ SEO Strategy &amp; Leadership | ✓ Technical &amp; On-page | ✓ Off-page &amp; Link Building | ✓ Search Console &amp; Analytics | ✓ Keyword Research | ✓ Remote | ✓ Fresh</t>
+          <t>✓ Role: GEO Specialist | ✓ SEO | ✓ GEO / AI Search | ✓ Remote</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6088,12 +6088,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Search Engine Optimization Executive</t>
+          <t>SEO/AEO/GEO Specialist</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>eBranding Studio - The Result-Oriented Digital Marketing Agency</t>
+          <t>Go Kite Travel and Tours</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -6103,7 +6103,7 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4472679783/</t>
+          <t>https://www.linkedin.com/jobs/view/4474661991/</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -6113,7 +6113,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Ahmedabad, Gujarat, India (Remote)</t>
+          <t>Kozhikode, Kerala, India (Remote)</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -6128,15 +6128,15 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
+          <t>2026-10-07 06:01</t>
         </is>
       </c>
       <c r="J93" s="4" t="n">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>✓ Title: search engine optimization | ✓ SEO | ✓ GEO / AI Search | ✓ Technical &amp; On-page | ✓ Off-page &amp; Link Building | ✓ Search Console &amp; Analytics | ✓ Keyword Research | ✓ Remote | ✓ Fresh</t>
+          <t>✓ Role: GEO Specialist | ✓ SEO | ✓ GEO / AI Search | ✓ Remote | ✓ Fresh</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -6149,12 +6149,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>SEO &amp; GEO Executive</t>
+          <t>SEO Specialist</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Tug Agency</t>
+          <t>Impressive</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -6164,7 +6164,7 @@
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4473754192/</t>
+          <t>https://www.linkedin.com/jobs/view/4462556649/</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -6174,12 +6174,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>London, England, United Kingdom (Remote)</t>
+          <t>Melbourne, Victoria, Australia (Remote)</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Consulting</t>
+          <t>Job</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -6189,15 +6189,15 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
+          <t>2026-10-07 06:01</t>
         </is>
       </c>
       <c r="J94" s="4" t="n">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>✓ Title: SEO | ✓ SEO | ✓ GEO / AI Search | ✓ Technical &amp; On-page | ✓ Keyword Research | ✓ Remote | ✓ Fresh</t>
+          <t>✓ Role: SEO Specialist | ✓ SEO | ✓ Remote | ✓ Fresh</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -6210,12 +6210,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>SEO, AEO &amp; GEO Specialist</t>
+          <t>Senior SEO Specialist</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Gyan Waar</t>
+          <t>Ultima Markets</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -6225,7 +6225,7 @@
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/jobs/view/4472128475/</t>
+          <t>https://www.linkedin.com/jobs/view/4475533404/</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -6235,12 +6235,12 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Gwalior, Madhya Pradesh, India (Remote)</t>
+          <t>WP. Kuala Lumpur, Federal Territory of Kuala Lumpur, Malaysia (Remote)</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Full-time</t>
+          <t>Job</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6250,15 +6250,15 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
+          <t>2026-10-07 06:01</t>
         </is>
       </c>
       <c r="J95" s="4" t="n">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>✓ Role: GEO Specialist | ✓ SEO | ✓ GEO / AI Search | ✓ Technical &amp; On-page | ✓ Off-page &amp; Link Building | ✓ Search Console &amp; Analytics | ✓ Keyword Research | ✓ WordPress / Ecommerce SEO | ✓ Remote | ✓ Fresh</t>
+          <t>✓ Role: SEO Specialist | ✓ SEO | ✓ Remote | ✓ Fresh</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -6271,30 +6271,34 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>سایت شرکتی</t>
+          <t>SEO Specialist - Dutch speaking</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>@ponisha_ir</t>
+          <t>Picnic Technologies</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>تلگرام — کانال‌های آگهی و پروژه</t>
+          <t>LinkedIn Jobs — SEO</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>https://ponisha.ir/project/760388/سایت-شرکتی</t>
+          <t>https://www.linkedin.com/jobs/view/4419851281/</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Website</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr"/>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Amsterdam, North Holland, Netherlands (Remote)</t>
+        </is>
+      </c>
       <c r="G96" t="inlineStr">
         <is>
           <t>Job</t>
@@ -6302,20 +6306,20 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
-        </is>
-      </c>
-      <c r="J96" t="n">
-        <v>34</v>
+          <t>2026-10-07 06:01</t>
+        </is>
+      </c>
+      <c r="J96" s="4" t="n">
+        <v>84</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>✓ SEO | ✓ WordPress / Ecommerce SEO | ✓ Fresh</t>
+          <t>✓ Role: SEO Specialist | ✓ SEO | ✓ Off-page &amp; Link Building | ✓ Search Console &amp; Analytics | ✓ Keyword Research | ✓ Remote</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -6328,22 +6332,22 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>سئو سایت فروشگاه اینترنتی و محصولات</t>
+          <t>Programmatic SEO Specialist</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>@ponisha_ir</t>
+          <t>Teamlex</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>تلگرام — کانال‌های آگهی و پروژه</t>
+          <t>LinkedIn Jobs — SEO</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>https://ponisha.ir/project/760382/سئو-سایت-فروشگاه-اینترنتی-و-محصولات</t>
+          <t>https://www.linkedin.com/jobs/view/4475343575/</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -6351,28 +6355,32 @@
           <t>SEO</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr"/>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Time, Rogaland, Norway (Remote)</t>
+        </is>
+      </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Freelance</t>
+          <t>Job</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
+          <t>2026-10-07 06:01</t>
         </is>
       </c>
       <c r="J97" s="4" t="n">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>✓ Title: سئو | ✓ SEO | ✓ Technical &amp; On-page | ✓ Off-page &amp; Link Building | ✓ Search Console &amp; Analytics | ✓ Keyword Research | ✓ WordPress / Ecommerce SEO | ✓ Freelance | ✓ Fresh</t>
+          <t>✓ Role: SEO Specialist | ✓ SEO | ✓ Technical &amp; On-page | ✓ Off-page &amp; Link Building | ✓ Search Console &amp; Analytics | ✓ Keyword Research | ✓ Remote</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -6385,22 +6393,22 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>سئو و رفع ایرادات ظاهری سایت کلینیک</t>
+          <t>Search Engine Optimization Executive</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>@ponisha_ir</t>
+          <t>TrafficHQ Digital Media LLP</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>تلگرام — کانال‌های آگهی و پروژه</t>
+          <t>LinkedIn Jobs — SEO</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>https://ponisha.ir/project/760352/سئو-و-رفع-ایرادات-ظاهری-سایت-کلینیک</t>
+          <t>https://www.linkedin.com/jobs/view/4468971844/</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -6408,28 +6416,32 @@
           <t>SEO</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr"/>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Mumbai, Maharashtra, India (Remote)</t>
+        </is>
+      </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
-        </is>
-      </c>
-      <c r="J98" s="3" t="n">
-        <v>54</v>
+          <t>2026-10-07 06:01</t>
+        </is>
+      </c>
+      <c r="J98" s="4" t="n">
+        <v>81</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>✓ Title: سئو | ✓ SEO | ✓ Search Console &amp; Analytics | ✓ WordPress / Ecommerce SEO | ✓ Fresh</t>
+          <t>✓ Title: search engine optimization | ✓ SEO | ✓ Technical &amp; On-page | ✓ Search Console &amp; Analytics | ✓ Keyword Research | ✓ Remote</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -6442,22 +6454,22 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>بررسی و اصلاح سئو سایت</t>
+          <t>Senior SEO Executive</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>@ponisha_ir</t>
+          <t>MG OMD</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>تلگرام — کانال‌های آگهی و پروژه</t>
+          <t>LinkedIn Jobs — SEO</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>https://ponisha.ir/project/760326/بررسی-و-اصلاح-سئو-سایت</t>
+          <t>https://www.linkedin.com/jobs/view/4474149575/</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -6465,7 +6477,11 @@
           <t>SEO</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr"/>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>London Area, United Kingdom (Remote)</t>
+        </is>
+      </c>
       <c r="G99" t="inlineStr">
         <is>
           <t>Collaboration</t>
@@ -6473,20 +6489,20 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
-        </is>
-      </c>
-      <c r="J99" s="3" t="n">
-        <v>53</v>
+          <t>2026-10-07 06:01</t>
+        </is>
+      </c>
+      <c r="J99" s="4" t="n">
+        <v>78</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>✓ Title: سئو | ✓ SEO | ✓ Off-page &amp; Link Building | ✓ Search Console &amp; Analytics | ✓ Fresh</t>
+          <t>✓ Title: SEO | ✓ SEO | ✓ SEO Strategy &amp; Leadership | ✓ Technical &amp; On-page | ✓ Search Console &amp; Analytics | ✓ Keyword Research | ✓ Remote</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -6499,51 +6515,55 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>طراحی وب‌سایت تک‌صفحه‌ای تعاملی و سه‌بعدی اسپیس کابین ماموت</t>
+          <t>SEO Executive</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>@ponisha_ir</t>
+          <t>Haystack</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>تلگرام — کانال‌های آگهی و پروژه</t>
+          <t>LinkedIn Jobs — SEO</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>https://ponisha.ir/project/760439/طراحی-وب‌سایت-تک‌صفحه‌ای-تعاملی-و-سه‌بعدی-اسپیس-کابین-ماموت</t>
+          <t>https://www.linkedin.com/jobs/view/4473403067/</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Website</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr"/>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Birmingham, England, United Kingdom (Remote)</t>
+        </is>
+      </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Freelance</t>
+          <t>Job</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
-        </is>
-      </c>
-      <c r="J100" t="n">
-        <v>40</v>
+          <t>2026-10-07 06:01</t>
+        </is>
+      </c>
+      <c r="J100" s="4" t="n">
+        <v>82</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>✓ SEO | ✓ Search Console &amp; Analytics | ✓ Freelance | ✓ Fresh</t>
+          <t>✓ Title: SEO | ✓ SEO | ✓ GEO / AI Search | ✓ SEO Strategy &amp; Leadership | ✓ Technical &amp; On-page | ✓ Search Console &amp; Analytics | ✓ Keyword Research | ✓ Remote</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -6556,51 +6576,55 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>بهینه سازی تخصصی وردپرس؛ مصرف بالای CPU و رفع خطای CLS</t>
+          <t>SEO Specialist</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>@ponisha_ir</t>
+          <t>11 Media Branding &amp; Marketing Agency</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>تلگرام — کانال‌های آگهی و پروژه</t>
+          <t>LinkedIn Jobs — SEO</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>https://ponisha.ir/project/760402/بهینه-سازی-تخصصی-وردپرس؛-مصرف-بالای-CPU-و-رفع-خطای-CLS</t>
+          <t>https://www.linkedin.com/jobs/view/4474246182/</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Website</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr"/>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Rajkot, Gujarat, India (Remote)</t>
+        </is>
+      </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Contract</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
-        </is>
-      </c>
-      <c r="J101" s="3" t="n">
-        <v>62</v>
+          <t>2026-10-07 06:01</t>
+        </is>
+      </c>
+      <c r="J101" s="4" t="n">
+        <v>91</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>✓ SEO | ✓ Technical &amp; On-page | ✓ Search Console &amp; Analytics | ✓ WordPress / Ecommerce SEO | ✓ Contract | ✓ Fresh</t>
+          <t>✓ Role: SEO Specialist | ✓ SEO | ✓ Technical &amp; On-page | ✓ Off-page &amp; Link Building | ✓ Search Console &amp; Analytics | ✓ Keyword Research | ✓ Remote | ✓ Fresh</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -6613,22 +6637,22 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>تحقیق کلمات کلیدی و تدوین برنامه محتوایی برای فروشگاه آنلاین</t>
+          <t>Seo Specialist</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>@ponisha_ir</t>
+          <t>clickzone - Growth Marketing Agency</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>تلگرام — کانال‌های آگهی و پروژه</t>
+          <t>LinkedIn Jobs — SEO</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>https://ponisha.ir/project/760526/تحقیق-کلمات-کلیدی-و-تدوین-برنامه-محتوایی-برای-فروشگاه-آنلاین</t>
+          <t>https://www.linkedin.com/jobs/view/4473498903/</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -6636,7 +6660,11 @@
           <t>SEO</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr"/>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Istanbul, Türkiye (Remote)</t>
+        </is>
+      </c>
       <c r="G102" t="inlineStr">
         <is>
           <t>Job</t>
@@ -6644,20 +6672,20 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
-        </is>
-      </c>
-      <c r="J102" t="n">
-        <v>44</v>
+          <t>2026-10-07 06:01</t>
+        </is>
+      </c>
+      <c r="J102" s="4" t="n">
+        <v>91</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>✓ SEO | ✓ Keyword Research | ✓ Fresh</t>
+          <t>✓ Role: SEO Specialist | ✓ SEO | ✓ Technical &amp; On-page | ✓ Off-page &amp; Link Building | ✓ Search Console &amp; Analytics | ✓ Keyword Research | ✓ Remote | ✓ Fresh</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -6670,22 +6698,22 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>طراحی و سئو سایت فروشگاهی</t>
+          <t>Specjalista ds. SEO</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>@ponisha_ir</t>
+          <t>Raven | Brands for Life</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>تلگرام — کانال‌های آگهی و پروژه</t>
+          <t>LinkedIn Jobs — SEO</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>https://ponisha.ir/project/760504/طراحی-و-سئو-سایت-فروشگاهی</t>
+          <t>https://www.linkedin.com/jobs/view/4473119327/</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -6693,7 +6721,11 @@
           <t>SEO</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr"/>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Cracow, Małopolskie, Poland (Remote)</t>
+        </is>
+      </c>
       <c r="G103" t="inlineStr">
         <is>
           <t>Job</t>
@@ -6701,20 +6733,20 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
+          <t>2026-10-07 06:01</t>
         </is>
       </c>
       <c r="J103" s="3" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>✓ Title: سئو | ✓ SEO | ✓ Technical &amp; On-page | ✓ Fresh</t>
+          <t>✓ Title: SEO | ✓ SEO | ✓ Remote</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -6727,22 +6759,22 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>همکاری با نویسنده محتوای پزشکی</t>
+          <t>Search Engine Optimization Executive</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>@ponisha_ir</t>
+          <t>Techflit Infotech LLP</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>تلگرام — کانال‌های آگهی و پروژه</t>
+          <t>LinkedIn Jobs — SEO</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>https://ponisha.ir/project/760498/همکاری-با-نویسنده-محتوای-پزشکی</t>
+          <t>https://www.linkedin.com/jobs/view/4472534594/</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -6750,7 +6782,11 @@
           <t>SEO</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr"/>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Surat, Gujarat, India (Remote)</t>
+        </is>
+      </c>
       <c r="G104" t="inlineStr">
         <is>
           <t>Collaboration</t>
@@ -6758,20 +6794,20 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
-        </is>
-      </c>
-      <c r="J104" t="n">
-        <v>28</v>
+          <t>2026-10-07 06:01</t>
+        </is>
+      </c>
+      <c r="J104" s="4" t="n">
+        <v>88</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>✓ SEO | ✓ Fresh</t>
+          <t>✓ Title: search engine optimization | ✓ SEO | ✓ GEO / AI Search | ✓ SEO Strategy &amp; Leadership | ✓ Technical &amp; On-page | ✓ Off-page &amp; Link Building | ✓ Search Console &amp; Analytics | ✓ Keyword Research | ✓ Remote</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -6784,22 +6820,22 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>سئو، امنیت و پشتیبانی سایت سالن اسپا</t>
+          <t>SEO Executive</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>@ponisha_ir</t>
+          <t>SunTec India</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>تلگرام — کانال‌های آگهی و پروژه</t>
+          <t>LinkedIn Jobs — SEO</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>https://ponisha.ir/project/760494/سئو،-امنیت-و-پشتیبانی-سایت-سالن-اسپا</t>
+          <t>https://www.linkedin.com/jobs/view/4472879507/</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -6807,28 +6843,32 @@
           <t>SEO</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr"/>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Noida, Uttar Pradesh, India (Remote)</t>
+        </is>
+      </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Job</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
-        </is>
-      </c>
-      <c r="J105" t="n">
-        <v>44</v>
+          <t>2026-10-07 06:01</t>
+        </is>
+      </c>
+      <c r="J105" s="4" t="n">
+        <v>77</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>✓ Title: سئو | ✓ SEO | ✓ Fresh</t>
+          <t>✓ Title: SEO | ✓ SEO | ✓ Technical &amp; On-page | ✓ Search Console &amp; Analytics | ✓ Keyword Research | ✓ Remote</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -6841,33 +6881,37 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>سئوی صفحه دسته‌بندی سایت فروشگاهی</t>
+          <t>Senior SEO Executive</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>@ponisha_ir</t>
+          <t>emap</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>تلگرام — کانال‌های آگهی و پروژه</t>
+          <t>LinkedIn Jobs — SEO</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>https://ponisha.ir/project/760481/سئوی-صفحه-دسته‌بندی-سایت-فروشگاهی</t>
+          <t>https://www.linkedin.com/jobs/view/4474253689/</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Website</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr"/>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>City Of London, England, United Kingdom (Remote)</t>
+        </is>
+      </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Job</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -6877,15 +6921,15 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
-        </is>
-      </c>
-      <c r="J106" t="n">
-        <v>34</v>
+          <t>2026-10-07 06:01</t>
+        </is>
+      </c>
+      <c r="J106" s="4" t="n">
+        <v>71</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>✓ SEO | ✓ Fresh</t>
+          <t>✓ Title: SEO | ✓ SEO | ✓ GEO / AI Search | ✓ Technical &amp; On-page | ✓ Search Console &amp; Analytics | ✓ Keyword Research | ✓ WordPress / Ecommerce SEO | ✓ Fresh</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -6898,30 +6942,34 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>طراحی و توسعه وب‌سایت شرکتی و صنعتی اختصاصی با PHP و Laravel</t>
+          <t>Specialista SEO</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>@ponisha_ir</t>
+          <t>Naxa | Agenzia di Marketing Strategico</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>تلگرام — کانال‌های آگهی و پروژه</t>
+          <t>LinkedIn Jobs — SEO</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>https://ponisha.ir/project/760468/طراحی-و-توسعه-وب‌سایت-شرکتی-و-صنعتی-اختصاصی-با-PHP-و-Laravel</t>
+          <t>https://www.linkedin.com/jobs/view/4474083309/</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Website</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr"/>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Bernareggio, Lombardy, Italy (Remote)</t>
+        </is>
+      </c>
       <c r="G107" t="inlineStr">
         <is>
           <t>Job</t>
@@ -6929,20 +6977,20 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
-        </is>
-      </c>
-      <c r="J107" t="n">
-        <v>38</v>
+          <t>2026-10-07 06:01</t>
+        </is>
+      </c>
+      <c r="J107" s="4" t="n">
+        <v>91</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>✓ SEO | ✓ WordPress / Ecommerce SEO | ✓ Fresh</t>
+          <t>✓ Title: SEO | ✓ SEO | ✓ GEO / AI Search | ✓ Technical &amp; On-page | ✓ Off-page &amp; Link Building | ✓ Search Console &amp; Analytics | ✓ Keyword Research | ✓ WordPress / Ecommerce SEO | ✓ Remote | ✓ Fresh</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -6955,51 +7003,55 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>طراحی قالب اختصاصی چندزبانه وردپرس صادرات صیفی‌جات</t>
+          <t>SEO Specialist (In-House)</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>@ponisha_ir</t>
+          <t>OOm Singapore</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>تلگرام — کانال‌های آگهی و پروژه</t>
+          <t>LinkedIn Jobs — SEO</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>https://ponisha.ir/project/760607/طراحی-قالب-اختصاصی-چندزبانه-وردپرس-صادرات-صیفی‌جات</t>
+          <t>https://www.linkedin.com/jobs/view/4476518752/</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Website</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr"/>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Singapore, Singapore (Remote)</t>
+        </is>
+      </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Freelance</t>
+          <t>Job</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
-        </is>
-      </c>
-      <c r="J108" t="n">
-        <v>41</v>
+          <t>2026-10-07 06:01</t>
+        </is>
+      </c>
+      <c r="J108" s="4" t="n">
+        <v>91</v>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>✓ SEO | ✓ WordPress / Ecommerce SEO | ✓ Freelance | ✓ Fresh</t>
+          <t>✓ Role: SEO Specialist | ✓ SEO | ✓ GEO / AI Search | ✓ SEO Strategy &amp; Leadership | ✓ Technical &amp; On-page | ✓ Off-page &amp; Link Building | ✓ Search Console &amp; Analytics | ✓ Keyword Research | ✓ Remote | ✓ Fresh</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -7012,51 +7064,55 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>به‌روزرسانی و سئوی سایت دفتر ترجمه</t>
+          <t>SEO Analyst</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>@ponisha_ir</t>
+          <t>Lantern Digital</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>تلگرام — کانال‌های آگهی و پروژه</t>
+          <t>LinkedIn Jobs — SEO</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>https://ponisha.ir/project/760554/به‌روزرسانی-و-سئوی-سایت-دفتر-ترجمه</t>
+          <t>https://www.linkedin.com/jobs/view/4473605718/</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Website</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr"/>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Ahmedabad, Gujarat, India (Remote)</t>
+        </is>
+      </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Job</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
-        </is>
-      </c>
-      <c r="J109" t="n">
-        <v>34</v>
+          <t>2026-10-07 06:01</t>
+        </is>
+      </c>
+      <c r="J109" s="4" t="n">
+        <v>81</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>✓ SEO | ✓ Fresh</t>
+          <t>✓ Title: SEO | ✓ SEO | ✓ Technical &amp; On-page | ✓ Off-page &amp; Link Building | ✓ Search Console &amp; Analytics | ✓ Keyword Research | ✓ Remote | ✓ Fresh</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -7069,51 +7125,55 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>اجرای سئوی محلی سایت خدمات آرایشگری</t>
+          <t>SEO Specialist till Google Partner i Halmstad</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>@ponisha_ir</t>
+          <t>Våning 18 AB</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>تلگرام — کانال‌های آگهی و پروژه</t>
+          <t>LinkedIn Jobs — SEO</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>https://ponisha.ir/project/760544/اجرای-سئوی-محلی-سایت-خدمات-آرایشگری</t>
+          <t>https://www.linkedin.com/jobs/view/4475158222/</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Website</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr"/>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Halmstad, Halland County, Sweden (Remote)</t>
+        </is>
+      </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Job</t>
+          <t>Collaboration</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
-        </is>
-      </c>
-      <c r="J110" t="n">
-        <v>40</v>
+          <t>2026-10-07 06:01</t>
+        </is>
+      </c>
+      <c r="J110" s="4" t="n">
+        <v>80</v>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>✓ SEO | ✓ Off-page &amp; Link Building | ✓ Fresh</t>
+          <t>✓ Role: SEO Specialist | ✓ SEO | ✓ Search Console &amp; Analytics | ✓ WordPress / Ecommerce SEO | ✓ Remote | ✓ Fresh</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -7126,22 +7186,22 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>تولید محتوا سئو محور</t>
+          <t>Senior SEO Specialist @ AEK Media</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>@karlancer_projects</t>
+          <t>Hatch</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>تلگرام — کانال‌های آگهی و پروژه</t>
+          <t>LinkedIn Jobs — SEO</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>https://www.karlancer.com/projects/تولید-محتوا-سئو-محور-w187wwero80r</t>
+          <t>https://www.linkedin.com/jobs/view/4452319274/</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -7149,28 +7209,32 @@
           <t>SEO</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr"/>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Sydney, New South Wales, Australia (Remote)</t>
+        </is>
+      </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Job</t>
+          <t>Collaboration</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
-        </is>
-      </c>
-      <c r="J111" t="n">
-        <v>43</v>
+          <t>2026-10-07 06:01</t>
+        </is>
+      </c>
+      <c r="J111" s="4" t="n">
+        <v>90</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>✓ Title: سئو | ✓ SEO | ✓ Fresh</t>
+          <t>✓ Role: SEO Specialist | ✓ SEO | ✓ Technical &amp; On-page | ✓ Search Console &amp; Analytics | ✓ Keyword Research | ✓ Remote | ✓ Fresh</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -7183,22 +7247,22 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>استخدام نویسنده محتوا برای همکاری با تیم سئو</t>
+          <t>SEO Executive</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>@karlancer_projects</t>
+          <t>Think Shaw</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>تلگرام — کانال‌های آگهی و پروژه</t>
+          <t>LinkedIn Jobs — SEO</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>https://www.karlancer.com/projects/استخدام-نویسنده-محتوا-برای-همکاری-تیم-سئو-906n557rn8ew</t>
+          <t>https://www.linkedin.com/jobs/view/4474254048/</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -7206,28 +7270,32 @@
           <t>SEO</t>
         </is>
       </c>
-      <c r="F112" t="inlineStr"/>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Sahibzada Ajit Singh Nagar, Punjab, India (Remote)</t>
+        </is>
+      </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Job</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
-        </is>
-      </c>
-      <c r="J112" t="n">
-        <v>38</v>
+          <t>2026-10-07 06:01</t>
+        </is>
+      </c>
+      <c r="J112" s="4" t="n">
+        <v>85</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>✓ Title: سئو | ✓ SEO | ✓ Fresh</t>
+          <t>✓ Title: SEO | ✓ SEO | ✓ GEO / AI Search | ✓ Technical &amp; On-page | ✓ Off-page &amp; Link Building | ✓ Search Console &amp; Analytics | ✓ Keyword Research | ✓ Remote | ✓ Fresh</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -7240,22 +7308,22 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>سئو کردن یک سری کلمات و یک ادرس سایت</t>
+          <t>SEO/AEO Expert</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>@karlancer_projects</t>
+          <t>Ninja Studio</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>تلگرام — کانال‌های آگهی و پروژه</t>
+          <t>LinkedIn Jobs — SEO</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>https://www.karlancer.com/projects/سئو-کردن-یک-سری-کلمات-یک-ادرس-سایت-2m6m22e49850</t>
+          <t>https://www.linkedin.com/jobs/view/4474046847/</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -7263,28 +7331,32 @@
           <t>SEO</t>
         </is>
       </c>
-      <c r="F113" t="inlineStr"/>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Dharamshala, Himachal Pradesh, India (Remote)</t>
+        </is>
+      </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Job</t>
+          <t>Collaboration</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
-        </is>
-      </c>
-      <c r="J113" t="n">
-        <v>47</v>
+          <t>2026-10-07 06:01</t>
+        </is>
+      </c>
+      <c r="J113" s="4" t="n">
+        <v>91</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>✓ Title: سئو | ✓ SEO | ✓ Fresh</t>
+          <t>✓ Title: SEO | ✓ SEO | ✓ GEO / AI Search | ✓ Technical &amp; On-page | ✓ Off-page &amp; Link Building | ✓ Search Console &amp; Analytics | ✓ Keyword Research | ✓ Remote | ✓ Fresh</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -7297,22 +7369,22 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>افزایش سرعت سایت، بازطراحی، سئو</t>
+          <t>Search Engine Optimization Executive</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>@karlancer_projects</t>
+          <t>VacationsPod</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>تلگرام — کانال‌های آگهی و پروژه</t>
+          <t>LinkedIn Jobs — SEO</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
         <is>
-          <t>https://www.karlancer.com/projects/افزایش-سرعت-سایت-بازطراحی-سئو-2564ee0o38n0</t>
+          <t>https://www.linkedin.com/jobs/view/4474912079/</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -7320,28 +7392,32 @@
           <t>SEO</t>
         </is>
       </c>
-      <c r="F114" t="inlineStr"/>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Sahibzada Ajit Singh Nagar, Punjab, India (Remote)</t>
+        </is>
+      </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Job</t>
+          <t>Full-time</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
-        </is>
-      </c>
-      <c r="J114" s="3" t="n">
-        <v>51</v>
+          <t>2026-10-07 06:01</t>
+        </is>
+      </c>
+      <c r="J114" s="4" t="n">
+        <v>91</v>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>✓ Title: سئو | ✓ SEO | ✓ WordPress / Ecommerce SEO | ✓ Fresh</t>
+          <t>✓ Title: search engine optimization | ✓ SEO | ✓ GEO / AI Search | ✓ Technical &amp; On-page | ✓ Off-page &amp; Link Building | ✓ Search Console &amp; Analytics | ✓ Keyword Research | ✓ WordPress / Ecommerce SEO | ✓ Remote | ✓ Fresh</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -7354,12 +7430,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>سئو تخصصی فروشگاه اینترنتی کفش، صندل و کفش اداری</t>
+          <t>تحلیل، برنامه‌ریزی و اجرای سئو سایت رایکانت</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>@karlancer_projects</t>
+          <t>@ponisha_ir</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -7369,7 +7445,7 @@
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>https://www.karlancer.com/projects/سئو-تخصصی-فروشگاه-اینترنتی-کفش-صندل-کفش-اداری-2m6m22m39850</t>
+          <t>https://ponisha.ir/project/760633/تحلیل،-برنامه‌ریزی-و-اجرای-سئو-سایت-رایکانت</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -7385,20 +7461,20 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
-        </is>
-      </c>
-      <c r="J115" t="n">
-        <v>47</v>
+          <t>2026-10-07 06:00</t>
+        </is>
+      </c>
+      <c r="J115" s="3" t="n">
+        <v>67</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>✓ Title: سئو | ✓ SEO | ✓ Fresh</t>
+          <t>✓ Title: سئو | ✓ SEO | ✓ Off-page &amp; Link Building | ✓ Search Console &amp; Analytics | ✓ Keyword Research | ✓ WordPress / Ecommerce SEO</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -7411,12 +7487,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>سئو سایت جذب متخصص SEO و GEO برای همکاری ماهانه و بلندمدت</t>
+          <t>طراحی سایت فروشگاهی</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>@karlancer_projects</t>
+          <t>@ponisha_ir</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -7426,36 +7502,36 @@
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>https://www.karlancer.com/projects/سئو-سایت-جذب-متخصص-seo-geo-برای-همکاری-1e82rre3383w</t>
+          <t>https://ponisha.ir/project/760696/طراحی-سایت-فروشگاهی</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>SEO</t>
+          <t>Website</t>
         </is>
       </c>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Collaboration</t>
+          <t>Freelance</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
-        </is>
-      </c>
-      <c r="J116" s="3" t="n">
-        <v>58</v>
+          <t>2026-10-07 06:00</t>
+        </is>
+      </c>
+      <c r="J116" t="n">
+        <v>32</v>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>✓ Title: SEO | ✓ SEO | ✓ GEO / AI Search | ✓ Fresh</t>
+          <t>✓ SEO | ✓ Freelance</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -7468,12 +7544,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>نیاز به ارتقا سایت دارم و به سئو کار خوب احتیاج دارم</t>
+          <t>گزارش SEO, GEO</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>@karlancer_projects</t>
+          <t>@ponisha_ir</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -7483,7 +7559,7 @@
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>https://www.karlancer.com/projects/نیاز-ارتقا-سایت-دارم-سئو-کار-خوب-احتیاج-1n6944e0382o</t>
+          <t>https://ponisha.ir/project/760675/گزارش-SEO,-GEO</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -7499,20 +7575,20 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>2026-10-01 06:00</t>
+          <t>2026-10-07 06:00</t>
         </is>
       </c>
       <c r="J117" s="3" t="n">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>✓ Title: سئو | ✓ SEO | ✓ Technical &amp; On-page | ✓ Fresh</t>
+          <t>✓ Title: SEO | ✓ SEO | ✓ GEO / AI Search | ✓ Off-page &amp; Link Building | ✓ Search Console &amp; Analytics | ✓ Keyword Research</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -7525,12 +7601,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>تولید ۱۲ مقاله سئو شده حرفه‌ای با تضمین رتبه صفحه اول گوگل</t>
+          <t>GEO / AEO / SEO برای اول شدن در نتایج ChatGPT و سایر AI</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>@karlancer_projects</t>
+          <t>@ponisha_ir</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -7540,7 +7616,7 @@
       </c>
       <c r="D118" s="2" t="inlineStr">
         <is>
-          <t>https://www.karlancer.com/projects/تولید-۱۲-مقاله-سئو-شده-حرفهای-تضمین-رتبه-7485222rm623</t>
+          <t>https://ponisha.ir/project/760669/GEO---AEO---SEO-برای-اول-شدن-در-نتایج-ChatGPT-و-سایر-AI</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -7556,31 +7632,2335 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>2026-10-07 06:00</t>
+        </is>
+      </c>
+      <c r="J118" s="4" t="n">
+        <v>73</v>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>✓ Title: SEO | ✓ SEO | ✓ GEO / AI Search | ✓ Search Console &amp; Analytics | ✓ WordPress / Ecommerce SEO</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>بارگذاری محصولات و تهیه محتوای معرفی در سایت</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>@ponisha_ir</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>تلگرام — کانال‌های آگهی و پروژه</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>https://ponisha.ir/project/760651/بارگذاری-محصولات-و-تهیه-محتوای-معرفی-در-سایت</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Collaboration</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>2026-10-07 06:00</t>
+        </is>
+      </c>
+      <c r="J119" t="n">
+        <v>23</v>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>✓ SEO</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>بررسی و اجرای اصلاحات سئو سایت فراثبت</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>@ponisha_ir</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>تلگرام — کانال‌های آگهی و پروژه</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>https://ponisha.ir/project/760764/بررسی-و-اجرای-اصلاحات-سئو-سایت-فراثبت</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Job</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
           <t>Unknown</t>
         </is>
       </c>
-      <c r="I118" t="inlineStr">
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>2026-10-07 06:00</t>
+        </is>
+      </c>
+      <c r="J120" t="n">
+        <v>47</v>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>✓ Title: سئو | ✓ SEO | ✓ Fresh</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>تغییر و توسعه فروشگاه اینترنتی فعال</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>@ponisha_ir</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>تلگرام — کانال‌های آگهی و پروژه</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>https://ponisha.ir/project/760761/تغییر-و-توسعه-فروشگاه-اینترنتی-فعال</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Job</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>2026-10-07 06:00</t>
+        </is>
+      </c>
+      <c r="J121" t="n">
+        <v>39</v>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>✓ SEO | ✓ WordPress / Ecommerce SEO | ✓ Fresh</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>سئوی سایت</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>@ponisha_ir</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>تلگرام — کانال‌های آگهی و پروژه</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>https://ponisha.ir/project/760709/سئوی-سایت</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Collaboration</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>2026-10-07 06:00</t>
+        </is>
+      </c>
+      <c r="J122" t="n">
+        <v>40</v>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>✓ SEO | ✓ Technical &amp; On-page | ✓ Search Console &amp; Analytics | ✓ WordPress / Ecommerce SEO</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2. سئوی صفر تا صد سایت فروشگاهی لوازم دیجیتال (نیازمند متخصص</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>@ponisha_ir</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>تلگرام — کانال‌های آگهی و پروژه</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>https://ponisha.ir/project/760799/2.-سئوی-صفر-تا-صد-سایت-فروشگاهی-لوازم-دیجیتال-(نیازمند-متخصص</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Collaboration</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>2026-10-07 06:00</t>
+        </is>
+      </c>
+      <c r="J123" t="n">
+        <v>40</v>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>✓ SEO | ✓ Technical &amp; On-page | ✓ Off-page &amp; Link Building | ✓ Search Console &amp; Analytics | ✓ WordPress / Ecommerce SEO | ✓ Fresh</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>بهبود رتبه سایت در کلمات کلیدی و رقابت با ترب در نتایج گوگل</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>@ponisha_ir</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>تلگرام — کانال‌های آگهی و پروژه</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>https://ponisha.ir/project/760797/بهبود-رتبه-سایت-در-کلمات-کلیدی-و-رقابت-با-ترب-در-نتایج-گوگل</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Collaboration</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>2026-10-07 06:00</t>
+        </is>
+      </c>
+      <c r="J124" t="n">
+        <v>40</v>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>✓ SEO | ✓ Technical &amp; On-page | ✓ Search Console &amp; Analytics | ✓ WordPress / Ecommerce SEO | ✓ Fresh</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>سئو سایت انجام شود</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>@ponisha_ir</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>تلگرام — کانال‌های آگهی و پروژه</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>https://ponisha.ir/project/760885/سئو-سایت-انجام-شود</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Collaboration</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>2026-10-07 06:00</t>
+        </is>
+      </c>
+      <c r="J125" s="3" t="n">
+        <v>54</v>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>✓ Title: سئو | ✓ SEO | ✓ Search Console &amp; Analytics | ✓ WordPress / Ecommerce SEO | ✓ Fresh</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>طراحی و بازطراحی کامل وب‌سایت</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>@ponisha_ir</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>تلگرام — کانال‌های آگهی و پروژه</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>https://ponisha.ir/project/760875/طراحی-و-بازطراحی-کامل-وب‌سایت</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr"/>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Freelance</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>2026-10-07 06:00</t>
+        </is>
+      </c>
+      <c r="J126" t="n">
+        <v>40</v>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>✓ SEO | ✓ WordPress / Ecommerce SEO | ✓ Freelance | ✓ Fresh</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>سئو سایت وردپرسی</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>@ponisha_ir</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>تلگرام — کانال‌های آگهی و پروژه</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>https://ponisha.ir/project/760874/سئو-سایت-وردپرسی</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr"/>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Collaboration</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>2026-10-07 06:00</t>
+        </is>
+      </c>
+      <c r="J127" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>✓ Title: سئو | ✓ SEO | ✓ Search Console &amp; Analytics | ✓ WordPress / Ecommerce SEO | ✓ Fresh</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>رفع مشکلات ایندکس و بهینه‌سازی سئوی فروشگاه وردپرسی</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>@ponisha_ir</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>تلگرام — کانال‌های آگهی و پروژه</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>https://ponisha.ir/project/760842/رفع-مشکلات-ایندکس-و-بهینه‌سازی-سئوی-فروشگاه-وردپرسی</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr"/>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Job</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>2026-10-07 06:00</t>
+        </is>
+      </c>
+      <c r="J128" t="n">
+        <v>40</v>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>✓ SEO | ✓ Search Console &amp; Analytics | ✓ WordPress / Ecommerce SEO | ✓ Fresh</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>نگارش مقاله سئو شده درباره تنهایی</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>@ponisha_ir</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>تلگرام — کانال‌های آگهی و پروژه</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>https://ponisha.ir/project/760918/نگارش-مقاله-سئو-شده-درباره-تنهایی</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Job</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>2026-10-07 06:00</t>
+        </is>
+      </c>
+      <c r="J129" t="n">
+        <v>49</v>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>✓ Title: سئو | ✓ SEO | ✓ Fresh</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>مقاله سئو‌شده درباره هنر بودن در تنهایی</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>@ponisha_ir</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>تلگرام — کانال‌های آگهی و پروژه</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>https://ponisha.ir/project/760914/مقاله-سئو‌شده-درباره-هنر-بودن-در-تنهایی</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Job</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>2026-10-07 06:00</t>
+        </is>
+      </c>
+      <c r="J130" t="n">
+        <v>49</v>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>✓ Title: سئو | ✓ SEO | ✓ Fresh</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>بهینه‌سازی فنی و سئوی تکنیکال سایت وردپرسی</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>@ponisha_ir</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>تلگرام — کانال‌های آگهی و پروژه</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>https://ponisha.ir/project/760898/بهینه‌سازی-فنی-و-سئوی-تکنیکال-سایت-وردپرسی</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr"/>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Freelance</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>2026-10-07 06:00</t>
+        </is>
+      </c>
+      <c r="J131" t="n">
+        <v>40</v>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>✓ SEO | ✓ Technical &amp; On-page | ✓ WordPress / Ecommerce SEO | ✓ Freelance | ✓ Fresh</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>طراحی سایت پزشکی با رعایت موارد اولیه سئو</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>@karlancer_projects</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>تلگرام — کانال‌های آگهی و پروژه</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>https://www.karlancer.com/projects/طراحی-سایت-پزشکی-رعایت-موارد-اولیه-سئو-1n69445eo82o</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr"/>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Job</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>2026-10-07 06:00</t>
+        </is>
+      </c>
+      <c r="J132" t="n">
+        <v>47</v>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>✓ Title: سئو | ✓ SEO | ✓ WordPress / Ecommerce SEO | ✓ Fresh</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>سئو سایت شرکت تجهیزات پزشکی</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>@karlancer_projects</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>تلگرام — کانال‌های آگهی و پروژه</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>https://www.karlancer.com/projects/سئو-سایت-شرکت-تجهیزات-پزشکی-e781rron76o1</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Job</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>2026-10-07 06:00</t>
+        </is>
+      </c>
+      <c r="J133" s="3" t="n">
+        <v>53</v>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>✓ Title: سئو | ✓ SEO | ✓ Off-page &amp; Link Building | ✓ Fresh</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>سئو و تولید محتوای تخصصی برای سایت آموزشگاه فنی و حرفه‌ای</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>@karlancer_projects</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>تلگرام — کانال‌های آگهی و پروژه</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>https://www.karlancer.com/projects/سئو-تولید-محتوای-تخصصی-برای-سایت-آموزشگاه-فنی-2564e4o538n0</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr"/>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Job</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>2026-10-07 06:00</t>
+        </is>
+      </c>
+      <c r="J134" t="n">
+        <v>47</v>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>✓ Title: سئو | ✓ SEO | ✓ Fresh</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>سئو یک سایت حوزه دیجیتال مارکتینگ</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>@karlancer_projects</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>تلگرام — کانال‌های آگهی و پروژه</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>https://www.karlancer.com/projects/سئو-یک-سایت-حوزه-دیجیتال-مارکتینگ-r78wrem3761w</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Job</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>2026-10-07 06:00</t>
+        </is>
+      </c>
+      <c r="J135" t="n">
+        <v>0</v>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>✗ Excluded: دیجیتال مارکتینگ</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>سئو سایت خدمات ساختمان الماس گیلان</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>@karlancer_projects</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>تلگرام — کانال‌های آگهی و پروژه</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>https://www.karlancer.com/projects/سئو-سایت-خدمات-ساختمان-الماس-گیلان-m080r75r784r</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr"/>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Job</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>2026-10-07 06:00</t>
+        </is>
+      </c>
+      <c r="J136" s="3" t="n">
+        <v>53</v>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>✓ Title: سئو | ✓ SEO | ✓ Search Console &amp; Analytics | ✓ Fresh</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>همکاری با متخصص SEO و Off-Page برای افزایش Domain Authority</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>@karlancer_projects</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>تلگرام — کانال‌های آگهی و پروژه</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>https://www.karlancer.com/projects/همکاری-متخصص-seo-offpage-برای-افزایش-domain-authority-906n5e9o78ew</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr"/>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Collaboration</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>2026-10-07 06:00</t>
+        </is>
+      </c>
+      <c r="J137" t="n">
+        <v>48</v>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>✓ Title: SEO | ✓ SEO | ✓ Off-page &amp; Link Building | ✓ Fresh</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>سئو محصولات در ترب و دیجی کالا</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>@karlancer_projects</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>تلگرام — کانال‌های آگهی و پروژه</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>https://www.karlancer.com/projects/سئو-محصولات-ترب-دیجی-کالا-74852o95e623</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr"/>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Job</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>2026-10-07 06:00</t>
+        </is>
+      </c>
+      <c r="J138" t="n">
+        <v>47</v>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>✓ Title: سئو | ✓ SEO | ✓ Fresh</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>سئو سایت خدماتی</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>@karlancer_projects</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>تلگرام — کانال‌های آگهی و پروژه</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>https://www.karlancer.com/projects/سئو-سایت-خدماتی-r78wremw261w</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr"/>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Job</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>2026-10-07 06:00</t>
+        </is>
+      </c>
+      <c r="J139" t="n">
+        <v>47</v>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>✓ Title: سئو | ✓ SEO | ✓ Fresh</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>دعوت به همکاری با تولیدکننده محتوای تخصصی حوزه لنت ترمز و دیسک و صفحه</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>@doorkaari</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>تلگرام — کانال‌های آگهی و پروژه</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>https://t.me/doorkaari/10859</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Collaboration</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>2026-10-07 06:00</t>
+        </is>
+      </c>
+      <c r="J140" t="n">
+        <v>37</v>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>✓ SEO | ✓ Off-page &amp; Link Building | ✓ Fresh</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>استخدام مدیر / متخصص ارشد سئو (Senior SEO Specialist) – تمام‌وقت</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>@doorkaari</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>تلگرام — کانال‌های آگهی و پروژه</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>https://t.me/doorkaari/10855</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>2026-10-07 06:00</t>
+        </is>
+      </c>
+      <c r="J141" s="4" t="n">
+        <v>88</v>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>✓ Role: SEO Specialist | ✓ SEO | ✓ GEO / AI Search | ✓ Technical &amp; On-page | ✓ Off-page &amp; Link Building | ✓ Search Console &amp; Analytics | ✓ Keyword Research | ✓ Remote</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>طراحی_سایت #وردپرس #انجام_دهنده</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>@doorkaari</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>تلگرام — کانال‌های آگهی و پروژه</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>https://t.me/doorkaari/10853</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Consulting</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>2026-10-07 06:00</t>
+        </is>
+      </c>
+      <c r="J142" t="n">
+        <v>26</v>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>✓ SEO | ✓ WordPress / Ecommerce SEO</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>استخدام متخصص سئو در دنیای ایده های تابان فناوری (داتک)</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>داتک</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>جستجوی وب (جابینجا)</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>https://jobinja.ir/companies/dotech/jobs/h4/</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>تهران</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Job</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>2026-10-01 06:01</t>
+        </is>
+      </c>
+      <c r="J143" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>✓ Role: متخصص سئو | ✓ SEO | ✓ Remote</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>استخدام متخصص سئو (SEO-دورکاری) در وبسایت ویزا 724</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>ویزا 724</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>جستجوی وب (جابینجا)</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>https://jobinja.ir/companies/visa724-com/jobs/RAmT/</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>ایران</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Full-time</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>2026-10-01 06:01</t>
+        </is>
+      </c>
+      <c r="J144" s="4" t="n">
+        <v>72</v>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>✓ Role: متخصص سئو | ✓ SEO | ✓ Search Console &amp; Analytics | ✓ Remote | ✓ ایران</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>استخدام کارشناس سئو (دورکاری) در بی هیرو</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>بی هیرو</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>جستجوی وب (جابینجا)</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>https://jobinja.ir/companies/be-hero/jobs/CMa1/</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>ایران</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Job</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>2026-10-01 06:01</t>
+        </is>
+      </c>
+      <c r="J145" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>✓ Role: کارشناس سئو | ✓ SEO | ✓ Remote | ✓ ایران</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>استخدام کارشناس سئو (SEO-دورکاری) در مارکت پیما</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>مارکت پیما</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>جستجوی وب (جابینجا)</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>https://jobinja.ir/companies/marketpeima/jobs/Jkv/</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>ایران</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Job</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>2026-10-01 06:01</t>
+        </is>
+      </c>
+      <c r="J146" s="4" t="n">
+        <v>77</v>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>✓ Role: کارشناس سئو | ✓ SEO | ✓ SEO Strategy &amp; Leadership | ✓ Remote | ✓ ایران</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Senior SEO Consultant cum strategist</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Expansion Desk</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>LinkedIn Jobs — SEO</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4472672640/</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Mumbai, Maharashtra, India (Remote)</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Consulting</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
         <is>
           <t>2026-10-01 06:00</t>
         </is>
       </c>
-      <c r="J118" t="n">
+      <c r="J147" s="4" t="n">
+        <v>70</v>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>✓ Role: SEO Consultant | ✓ SEO | ✓ Remote | ✓ Fresh</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Search Engine Optimization Executive</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>eBranding Studio - The Result-Oriented Digital Marketing Agency</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>LinkedIn Jobs — SEO</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/jobs/view/4472679783/</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Ahmedabad, Gujarat, India (Remote)</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Job</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Remote</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>2026-10-01 06:00</t>
+        </is>
+      </c>
+      <c r="J148" s="4" t="n">
+        <v>91</v>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>✓ Title: search engine optimization | ✓ SEO | ✓ GEO / AI Search | ✓ Technical &amp; On-page | ✓ Off-page &amp; Link Building | ✓ Search Console &amp; Analytics | ✓ Keyword Research | ✓ Remote | ✓ Fresh</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>طراحی قالب اختصاصی چندزبانه وردپرس صادرات صیفی‌جات</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>@ponisha_ir</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>تلگرام — کانال‌های آگهی و پروژه</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>https://ponisha.ir/project/760607/طراحی-قالب-اختصاصی-چندزبانه-وردپرس-صادرات-صیفی‌جات</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Freelance</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>2026-10-01 06:00</t>
+        </is>
+      </c>
+      <c r="J149" t="n">
+        <v>41</v>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>✓ SEO | ✓ WordPress / Ecommerce SEO | ✓ Freelance | ✓ Fresh</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>به‌روزرسانی و سئوی سایت دفتر ترجمه</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>@ponisha_ir</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>تلگرام — کانال‌های آگهی و پروژه</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
+        <is>
+          <t>https://ponisha.ir/project/760554/به‌روزرسانی-و-سئوی-سایت-دفتر-ترجمه</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Job</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>2026-10-01 06:00</t>
+        </is>
+      </c>
+      <c r="J150" t="n">
+        <v>34</v>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>✓ SEO | ✓ Fresh</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>اجرای سئوی محلی سایت خدمات آرایشگری</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>@ponisha_ir</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>تلگرام — کانال‌های آگهی و پروژه</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
+        <is>
+          <t>https://ponisha.ir/project/760544/اجرای-سئوی-محلی-سایت-خدمات-آرایشگری</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Job</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Hybrid</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>2026-10-01 06:00</t>
+        </is>
+      </c>
+      <c r="J151" t="n">
+        <v>40</v>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>✓ SEO | ✓ Off-page &amp; Link Building | ✓ Fresh</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>استخدام نویسنده محتوا برای همکاری با تیم سئو</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>@karlancer_projects</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>تلگرام — کانال‌های آگهی و پروژه</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>https://www.karlancer.com/projects/استخدام-نویسنده-محتوا-برای-همکاری-تیم-سئو-906n557rn8ew</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Collaboration</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>2026-10-01 06:00</t>
+        </is>
+      </c>
+      <c r="J152" t="n">
+        <v>38</v>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>✓ Title: سئو | ✓ SEO | ✓ Fresh</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>سئو کردن یک سری کلمات و یک ادرس سایت</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>@karlancer_projects</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>تلگرام — کانال‌های آگهی و پروژه</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
+        <is>
+          <t>https://www.karlancer.com/projects/سئو-کردن-یک-سری-کلمات-یک-ادرس-سایت-2m6m22e49850</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Job</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>2026-10-01 06:00</t>
+        </is>
+      </c>
+      <c r="J153" t="n">
+        <v>47</v>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>✓ Title: سئو | ✓ SEO | ✓ Fresh</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>افزایش سرعت سایت، بازطراحی، سئو</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>@karlancer_projects</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>تلگرام — کانال‌های آگهی و پروژه</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
+        <is>
+          <t>https://www.karlancer.com/projects/افزایش-سرعت-سایت-بازطراحی-سئو-2564ee0o38n0</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Job</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>2026-10-01 06:00</t>
+        </is>
+      </c>
+      <c r="J154" s="3" t="n">
+        <v>51</v>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>✓ Title: سئو | ✓ SEO | ✓ WordPress / Ecommerce SEO | ✓ Fresh</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>سئو تخصصی فروشگاه اینترنتی کفش، صندل و کفش اداری</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>@karlancer_projects</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>تلگرام — کانال‌های آگهی و پروژه</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>https://www.karlancer.com/projects/سئو-تخصصی-فروشگاه-اینترنتی-کفش-صندل-کفش-اداری-2m6m22m39850</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Job</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>2026-10-01 06:00</t>
+        </is>
+      </c>
+      <c r="J155" t="n">
+        <v>47</v>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>✓ Title: سئو | ✓ SEO | ✓ Fresh</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>سئو سایت جذب متخصص SEO و GEO برای همکاری ماهانه و بلندمدت</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>@karlancer_projects</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>تلگرام — کانال‌های آگهی و پروژه</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
+        <is>
+          <t>https://www.karlancer.com/projects/سئو-سایت-جذب-متخصص-seo-geo-برای-همکاری-1e82rre3383w</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr"/>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Collaboration</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>2026-10-01 06:00</t>
+        </is>
+      </c>
+      <c r="J156" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>✓ Title: SEO | ✓ SEO | ✓ GEO / AI Search | ✓ Fresh</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>نیاز به ارتقا سایت دارم و به سئو کار خوب احتیاج دارم</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>@karlancer_projects</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>تلگرام — کانال‌های آگهی و پروژه</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
+        <is>
+          <t>https://www.karlancer.com/projects/نیاز-ارتقا-سایت-دارم-سئو-کار-خوب-احتیاج-1n6944e0382o</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr"/>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Job</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>2026-10-01 06:00</t>
+        </is>
+      </c>
+      <c r="J157" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>✓ Title: سئو | ✓ SEO | ✓ Technical &amp; On-page | ✓ Fresh</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>تولید ۱۲ مقاله سئو شده حرفه‌ای با تضمین رتبه صفحه اول گوگل</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>@karlancer_projects</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>تلگرام — کانال‌های آگهی و پروژه</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>https://www.karlancer.com/projects/تولید-۱۲-مقاله-سئو-شده-حرفهای-تضمین-رتبه-7485222rm623</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>SEO</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Job</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>2026-10-01 06:00</t>
+        </is>
+      </c>
+      <c r="J158" t="n">
         <v>43</v>
       </c>
-      <c r="K118" t="inlineStr">
+      <c r="K158" t="inlineStr">
         <is>
           <t>✓ Title: سئو | ✓ SEO | ✓ Fresh</t>
         </is>
       </c>
-      <c r="L118" t="inlineStr">
-        <is>
-          <t>New</t>
-        </is>
-      </c>
-      <c r="M118" t="inlineStr"/>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M118"/>
+  <autoFilter ref="A1:M158"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D3" r:id="rId2"/>
@@ -7699,6 +10079,46 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D116" r:id="rId115"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D117" r:id="rId116"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D158" r:id="rId157"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
